--- a/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
+++ b/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Project/glucolink-a2/docs/excel_reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEDADE2-76F4-5244-82FE-320AB97A2928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F21E68-DE4D-4442-A2EC-F1F05C410E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="680" windowWidth="24120" windowHeight="19960" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="620" windowWidth="25600" windowHeight="19280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="129">
   <si>
     <t>GlucoLink reporting export — template</t>
   </si>
@@ -97,9 +97,6 @@
     <t>UC1 rows</t>
   </si>
   <si>
-    <t>NOT RUN</t>
-  </si>
-  <si>
     <t>UC2 rows</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>UC2 rows 11, NON_ADHERENT 2; ADHERENT 9</t>
-  </si>
-  <si>
     <t>GL-0001</t>
   </si>
   <si>
@@ -344,6 +338,87 @@
   </si>
   <si>
     <t>Ethan Lewis</t>
+  </si>
+  <si>
+    <t>Parramatta Family Practice</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>HIGH_NO_REVIEW</t>
+  </si>
+  <si>
+    <t>HIGH_REVIEW_PENDING</t>
+  </si>
+  <si>
+    <t>Blacktown Medical Centre</t>
+  </si>
+  <si>
+    <t>OVERDUE_TEST</t>
+  </si>
+  <si>
+    <t>GL-0006</t>
+  </si>
+  <si>
+    <t>NO_TEST_ON_RECORD</t>
+  </si>
+  <si>
+    <t>GL-0014</t>
+  </si>
+  <si>
+    <t>Noah Harris</t>
+  </si>
+  <si>
+    <t>Penrith GP Clinic</t>
+  </si>
+  <si>
+    <t>RISING</t>
+  </si>
+  <si>
+    <t>STABLE</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_HISTORY</t>
+  </si>
+  <si>
+    <t>GL-0004</t>
+  </si>
+  <si>
+    <t>Olivia Brown</t>
+  </si>
+  <si>
+    <t>GL-0011</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>GL-0013</t>
+  </si>
+  <si>
+    <t>Chloe White</t>
+  </si>
+  <si>
+    <t>GL-0015</t>
+  </si>
+  <si>
+    <t>Ava Robinson</t>
+  </si>
+  <si>
+    <t>RESULT_NOT_RETURNED</t>
+  </si>
+  <si>
+    <t>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</t>
+  </si>
+  <si>
+    <t>MULTI_PHARMACY_OVERLAP</t>
+  </si>
+  <si>
+    <t>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</t>
+  </si>
+  <si>
+    <t>4/20/26</t>
   </si>
 </sst>
 </file>
@@ -353,7 +428,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +446,11 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -413,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -423,6 +503,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -859,131 +941,151 @@
       <c r="B4" s="2">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2">
         <v>16</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2">
+        <v>16</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1002,42 +1104,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="28" customWidth="1"/>
@@ -1055,28 +1157,236 @@
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>55</v>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46162</v>
+      </c>
+      <c r="E2" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46204</v>
+      </c>
+      <c r="E3" s="3">
+        <v>58</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E4" s="3">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46054</v>
+      </c>
+      <c r="E6" s="3">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E7" s="3">
+        <v>57</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46244</v>
+      </c>
+      <c r="E8" s="3">
+        <v>58</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E9" s="3">
+        <v>65</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>
@@ -1095,48 +1405,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D2" s="3">
         <v>7</v>
@@ -1151,7 +1461,7 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I2" s="4">
         <v>46086</v>
@@ -1165,13 +1475,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="3">
         <v>3</v>
@@ -1186,7 +1496,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I3" s="4">
         <v>46086</v>
@@ -1200,13 +1510,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3">
         <v>6</v>
@@ -1221,7 +1531,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I4" s="4">
         <v>46086</v>
@@ -1235,13 +1545,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3">
         <v>8</v>
@@ -1256,7 +1566,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I5" s="4">
         <v>46086</v>
@@ -1270,13 +1580,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -1291,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I6" s="4">
         <v>46086</v>
@@ -1305,13 +1615,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
@@ -1326,7 +1636,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I7" s="4">
         <v>46086</v>
@@ -1340,13 +1650,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
@@ -1361,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I8" s="4">
         <v>46086</v>
@@ -1375,13 +1685,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -1396,7 +1706,7 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I9" s="4">
         <v>46086</v>
@@ -1410,13 +1720,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3">
         <v>6</v>
@@ -1431,7 +1741,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I10" s="4">
         <v>46086</v>
@@ -1445,13 +1755,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="D11" s="3">
         <v>7</v>
@@ -1466,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I11" s="4">
         <v>46086</v>
@@ -1480,13 +1790,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3">
         <v>6</v>
@@ -1501,7 +1811,7 @@
         <v>0.91700000000000004</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="4">
         <v>46086</v>
@@ -1521,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="12" width="28" customWidth="1"/>
@@ -1529,40 +1839,648 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="3">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45940</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46162</v>
+      </c>
+      <c r="G2" s="3">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45981</v>
+      </c>
+      <c r="E3" s="3">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G3" s="3">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E4" s="3">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G4" s="3">
+        <v>51</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E5" s="3">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G5" s="3">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46027</v>
+      </c>
+      <c r="E6" s="3">
+        <v>50.8</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46147</v>
+      </c>
+      <c r="G6" s="3">
+        <v>51.9</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="E7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="3">
+        <v>51</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46198</v>
+      </c>
+      <c r="G8" s="3">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <v>45928</v>
+      </c>
+      <c r="E9" s="3">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F9" s="4">
+        <v>46201</v>
+      </c>
+      <c r="G9" s="3">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="G10" s="3">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E11" s="3">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46193</v>
+      </c>
+      <c r="G11" s="3">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-4</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="G12" s="3">
+        <v>57</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>45971</v>
+      </c>
+      <c r="E13" s="3">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G13" s="3">
+        <v>60</v>
+      </c>
+      <c r="H13" s="3">
+        <v>5</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46063</v>
+      </c>
+      <c r="E14" s="3">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46244</v>
+      </c>
+      <c r="G14" s="3">
+        <v>58</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G15" s="3">
+        <v>50</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45966</v>
+      </c>
+      <c r="E16" s="3">
+        <v>53</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46178</v>
+      </c>
+      <c r="G16" s="3">
         <v>65</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>55</v>
+      <c r="H16" s="3">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="3">
+        <v>49</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G17" s="3">
+        <v>49</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="K17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>
@@ -1573,7 +2491,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="28" customWidth="1"/>
@@ -1581,19 +2499,53 @@
   <sheetData>
     <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
+++ b/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
@@ -8,41 +8,80 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Project/glucolink-a2/docs/excel_reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F21E68-DE4D-4442-A2EC-F1F05C410E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BAC49-4570-CC41-83F3-D51EA4CB1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="620" windowWidth="25600" windowHeight="19280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="20160" windowHeight="19280" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
     <sheet name="Checks" sheetId="2" r:id="rId2"/>
     <sheet name="Queries" sheetId="3" r:id="rId3"/>
-    <sheet name="UC1" sheetId="4" r:id="rId4"/>
-    <sheet name="UC2" sheetId="5" r:id="rId5"/>
-    <sheet name="UC3" sheetId="6" r:id="rId6"/>
-    <sheet name="UC4" sheetId="7" r:id="rId7"/>
+    <sheet name="UC1 Dashboard" sheetId="8" r:id="rId4"/>
+    <sheet name="UC2 Dashboard" sheetId="9" r:id="rId5"/>
+    <sheet name="UC3 Dashboard" sheetId="10" r:id="rId6"/>
+    <sheet name="UC4 Dashboard" sheetId="11" r:id="rId7"/>
+    <sheet name="UC1" sheetId="4" r:id="rId8"/>
+    <sheet name="UC2" sheetId="5" r:id="rId9"/>
+    <sheet name="UC3" sheetId="6" r:id="rId10"/>
+    <sheet name="UC4" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UC1'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'UC2'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'UC3'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'UC4'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'UC1'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'UC2'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'UC3'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UC4'!$A$1:$E$1</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'UC1 Dashboard'!$B$5</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'UC1 Dashboard'!$B$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="129">
-  <si>
-    <t>GlucoLink reporting export — template</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="163">
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>NOT LOADED — no reporting data included</t>
-  </si>
-  <si>
     <t>Database</t>
   </si>
   <si>
@@ -418,17 +457,127 @@
     <t>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</t>
   </si>
   <si>
-    <t>4/20/26</t>
+    <t>LOADED: all four views from one read-only snapshot of the frozen database</t>
+  </si>
+  <si>
+    <t>glucolink_a2 (shared PostgreSQL 15.19 server, CloudBeaver connection 'GlucoLink A2 - Team')</t>
+  </si>
+  <si>
+    <t>9a499ce (frozen SQL 00 to 09; shared DB rebuilt from it on 11 Oct 2026)</t>
+  </si>
+  <si>
+    <t>2026-10-14 17:12 ; all four views in the same session</t>
+  </si>
+  <si>
+    <t>Read-only SELECT statements from the Queries sheet, run through CloudBeaver on glucolink_a2. Consistent snapshot: yes. The database is frozen (SELECT only) since the 11 Oct rebuild.</t>
+  </si>
+  <si>
+    <t>Minha Kim, 2026-10-14</t>
+  </si>
+  <si>
+    <t>GlucoLink reporting export</t>
+  </si>
+  <si>
+    <t>Rule parameters (actual, reporting.rule_parameter)</t>
+  </si>
+  <si>
+    <t>param_name</t>
+  </si>
+  <si>
+    <t>param_value</t>
+  </si>
+  <si>
+    <t>2026_09_01</t>
+  </si>
+  <si>
+    <t>hba1c_high_mmol</t>
+  </si>
+  <si>
+    <t>pdc_threshold</t>
+  </si>
+  <si>
+    <t>pdc_window_days</t>
+  </si>
+  <si>
+    <t>return_grace_days</t>
+  </si>
+  <si>
+    <t>review_window_days</t>
+  </si>
+  <si>
+    <t>test_overdue_months</t>
+  </si>
+  <si>
+    <t>trend_min_change_mmol</t>
+  </si>
+  <si>
+    <t>trend_window_months</t>
+  </si>
+  <si>
+    <t>Automated tests (audit.test_results)</t>
+  </si>
+  <si>
+    <t>46 run, 46 passed, 0 failed</t>
+  </si>
+  <si>
+    <t>UC1 Care gaps: patient per care-gap status</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_uc1_care_gaps | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
+  </si>
+  <si>
+    <t>patients</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>UC2 Medication adherence: PDC per patient (threshold 0.8)</t>
+  </si>
+  <si>
+    <t>patient (sorted by PDC)</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_uc2_pdc | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
+  </si>
+  <si>
+    <t>UC3 HbA1c trend: change in HbA1c per patient</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>Practice nurse: book an HbA1c test for overdue or untested patients, and a GP review for high results with no review.</t>
+  </si>
+  <si>
+    <t>Community pharmacist: contact NON_ADHERENT patients (PDC below 0.8) about refills and barriers to taking their medication.</t>
+  </si>
+  <si>
+    <t>GP: review treatment for RISING patients; * = rising despite adherence, so consider a change of therapy rather than an adherence talk.</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_HISTORY (fewer than 2 tests) has no change value, so it has no bar; it is not drawn as zero. FALLING: 0 patients.</t>
+  </si>
+  <si>
+    <t>UC4 Care-path breaks: breaks per type</t>
+  </si>
+  <si>
+    <t>GlucoLink network care coordinator: ask the lab to resend the missing result to the clinic, and contact the patient and both pharmacies about the overlapping supply.</t>
+  </si>
+  <si>
+    <t>breaks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="171" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="173" formatCode="\+0.00;\-0.00;0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,8 +601,38 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20334C"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,8 +644,14 @@
         <fgColor rgb="FF19334D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -489,11 +674,181 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -505,6 +860,86 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,6 +955,4258 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>patients per care-gap status (n = 8)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC1 Dashboard'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>patients</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC1 Dashboard'!$A$6:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>HIGH_NO_REVIEW</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HIGH_REVIEW_PENDING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>OVERDUE_TEST</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>NO_TEST_ON_RECORD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC1 Dashboard'!$B$6:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1564980800"/>
+        <c:axId val="1564982144"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1564980800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564982144"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1564982144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564980800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>PDC</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>per. atient,</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>lowest</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>first</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-AU" altLang="ko-KR" baseline="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADHERENT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$A$6:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>GL-0002 Mei Chen (0.333)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0010 William Jones (0.500)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0017 Ethan Lewis (0.917)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0005 James Wilson (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0012 Lucas Martin (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0003 Ahmed Khan (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008 Sarah Lee (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0001 Thomas Smith (0.989)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0007 Daniel Nguyen (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0009 Grace Taylor (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0016 Zoe Clark (1.000)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC2 Dashboard'!$D$6:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.98899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E39B-5D49-B21B-4ABC7832F6BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NON_ADHERENT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$A$6:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>GL-0002 Mei Chen (0.333)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0010 William Jones (0.500)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0017 Ethan Lewis (0.917)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0005 James Wilson (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0012 Lucas Martin (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0003 Ahmed Khan (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008 Sarah Lee (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0001 Thomas Smith (0.989)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0007 Daniel Nguyen (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0009 Grace Taylor (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0016 Zoe Clark (1.000)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC2 Dashboard'!$E$6:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.33300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E39B-5D49-B21B-4ABC7832F6BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="1647495808"/>
+        <c:axId val="1647498496"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1647495808"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1647498496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1647498496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1647495808"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-AU" sz="1800">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>HbA1c change from first to last test (mmol/mol) </a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-AU" sz="1800">
+                <a:effectLst/>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-AU" sz="1000">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>* = rising despite adherence</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-AU" sz="1800">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RISING</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$A$6:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>GL-0001 *</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0003 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0007 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0010 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0011</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0012 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>GL-0013</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>GL-0014</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>GL-0015</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>GL-0016 *</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>GL-0017 (1 test)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC3 Dashboard'!$D$6:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>\+0.00;\-0.00;0</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-46CD-AF41-96F6-6302E5C7632C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>STABLE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$A$6:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>GL-0001 *</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0003 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0007 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0010 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0011</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0012 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>GL-0013</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>GL-0014</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>GL-0015</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>GL-0016 *</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>GL-0017 (1 test)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC3 Dashboard'!$E$6:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>\+0.00;\-0.00;0</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-46CD-AF41-96F6-6302E5C7632C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="50"/>
+        <c:overlap val="100"/>
+        <c:axId val="1564609600"/>
+        <c:axId val="1564621248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1564609600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564621248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1564621248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\+0.00;\-0.00;0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564609600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Care-path</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> breaks per type (n = 2)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC4 Dashboard'!$A$6:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>RESULT_NOT_RETURNED</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MULTI_PHARMACY_OVERLAP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC4 Dashboard'!$B$6:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DA3B-4B43-A83E-629B9770251D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1592126400"/>
+        <c:axId val="1592123712"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1592126400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592123712"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1592123712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592126400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC75E2A0-F94B-714A-ADDA-81BEB6C4925D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CC09AC4-8487-83F7-0042-2313374AB9C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C052620-A1BC-7C3A-DA80-C34BAF1440A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02BB58DA-F14D-5A7C-0E3C-914F20845540}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -807,7 +5494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -816,79 +5503,910 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46266</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45940</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46162</v>
+      </c>
+      <c r="G2" s="3">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45981</v>
+      </c>
+      <c r="E3" s="3">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G3" s="3">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E4" s="3">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G4" s="3">
+        <v>51</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E5" s="3">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G5" s="3">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46027</v>
+      </c>
+      <c r="E6" s="3">
+        <v>50.8</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46147</v>
+      </c>
+      <c r="G6" s="3">
+        <v>51.9</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="E7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="3">
+        <v>51</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46198</v>
+      </c>
+      <c r="G8" s="3">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <v>45928</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46201</v>
+      </c>
+      <c r="G9" s="3">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="G10" s="3">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E11" s="3">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46193</v>
+      </c>
+      <c r="G11" s="3">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-4</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="G12" s="3">
+        <v>57</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>45971</v>
+      </c>
+      <c r="E13" s="3">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G13" s="3">
+        <v>60</v>
+      </c>
+      <c r="H13" s="3">
+        <v>5</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46063</v>
+      </c>
+      <c r="E14" s="3">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46244</v>
+      </c>
+      <c r="G14" s="3">
+        <v>58</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G15" s="3">
+        <v>50</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45966</v>
+      </c>
+      <c r="E16" s="3">
+        <v>53</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46178</v>
+      </c>
+      <c r="G16" s="3">
+        <v>65</v>
+      </c>
+      <c r="H16" s="3">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="3">
+        <v>49</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G17" s="3">
+        <v>49</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="K17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46132</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -906,7 +6424,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -914,7 +6432,7 @@
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -922,21 +6440,21 @@
     </row>
     <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <v>8</v>
@@ -945,12 +6463,12 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <v>11</v>
@@ -959,12 +6477,12 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
         <v>16</v>
@@ -973,12 +6491,12 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -987,54 +6505,54 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1043,49 +6561,49 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1104,42 +6622,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1148,6 +6666,1516 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A92C5B-52A4-FE4D-B226-05D025B6D1B7}">
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="21">
+        <f>SUM(B6:B9)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>IF('UC1'!A2="","",'UC1'!A2)</f>
+        <v>GL-0001</v>
+      </c>
+      <c r="B27" t="str">
+        <f>IF('UC1'!B2="","",'UC1'!B2)</f>
+        <v>Thomas Smith</v>
+      </c>
+      <c r="C27" t="str">
+        <f>IF('UC1'!C2="","",'UC1'!C2)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D27" s="25">
+        <f>IF('UC1'!D2="","",'UC1'!D2)</f>
+        <v>46162</v>
+      </c>
+      <c r="E27">
+        <f>IF('UC1'!E2="","",'UC1'!E2)</f>
+        <v>62</v>
+      </c>
+      <c r="F27" t="str">
+        <f>IF('UC1'!F2="","",'UC1'!F2)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF('UC1'!G2="","",'UC1'!G2)</f>
+        <v>HIGH_NO_REVIEW</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>IF('UC1'!A3="","",'UC1'!A3)</f>
+        <v>GL-0002</v>
+      </c>
+      <c r="B28" t="str">
+        <f>IF('UC1'!B3="","",'UC1'!B3)</f>
+        <v>Mei Chen</v>
+      </c>
+      <c r="C28" t="str">
+        <f>IF('UC1'!C3="","",'UC1'!C3)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D28" s="25">
+        <f>IF('UC1'!D3="","",'UC1'!D3)</f>
+        <v>46204</v>
+      </c>
+      <c r="E28">
+        <f>IF('UC1'!E3="","",'UC1'!E3)</f>
+        <v>58</v>
+      </c>
+      <c r="G28" t="str">
+        <f>IF('UC1'!G3="","",'UC1'!G3)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>IF('UC1'!A4="","",'UC1'!A4)</f>
+        <v>GL-0003</v>
+      </c>
+      <c r="B29" t="str">
+        <f>IF('UC1'!B4="","",'UC1'!B4)</f>
+        <v>Ahmed Khan</v>
+      </c>
+      <c r="C29" t="str">
+        <f>IF('UC1'!C4="","",'UC1'!C4)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D29" s="25">
+        <f>IF('UC1'!D4="","",'UC1'!D4)</f>
+        <v>45992</v>
+      </c>
+      <c r="E29">
+        <f>IF('UC1'!E4="","",'UC1'!E4)</f>
+        <v>51</v>
+      </c>
+      <c r="G29" t="str">
+        <f>IF('UC1'!G4="","",'UC1'!G4)</f>
+        <v>OVERDUE_TEST</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f>IF('UC1'!A5="","",'UC1'!A5)</f>
+        <v>GL-0006</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF('UC1'!B5="","",'UC1'!B5)</f>
+        <v>Daniel Nguyen</v>
+      </c>
+      <c r="C30" t="str">
+        <f>IF('UC1'!C5="","",'UC1'!C5)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D30" s="25" t="str">
+        <f>IF('UC1'!D5="","",'UC1'!D5)</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF('UC1'!E5="","",'UC1'!E5)</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>IF('UC1'!G5="","",'UC1'!G5)</f>
+        <v>NO_TEST_ON_RECORD</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
+        <f>IF('UC1'!A6="","",'UC1'!A6)</f>
+        <v>GL-0010</v>
+      </c>
+      <c r="B31" t="str">
+        <f>IF('UC1'!B6="","",'UC1'!B6)</f>
+        <v>William Jones</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF('UC1'!C6="","",'UC1'!C6)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D31" s="25">
+        <f>IF('UC1'!D6="","",'UC1'!D6)</f>
+        <v>46054</v>
+      </c>
+      <c r="E31">
+        <f>IF('UC1'!E6="","",'UC1'!E6)</f>
+        <v>52</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF('UC1'!G6="","",'UC1'!G6)</f>
+        <v>OVERDUE_TEST</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF('UC1'!A7="","",'UC1'!A7)</f>
+        <v>GL-0012</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF('UC1'!B7="","",'UC1'!B7)</f>
+        <v>Lucas Martin</v>
+      </c>
+      <c r="C32" t="str">
+        <f>IF('UC1'!C7="","",'UC1'!C7)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D32" s="25">
+        <f>IF('UC1'!D7="","",'UC1'!D7)</f>
+        <v>46152</v>
+      </c>
+      <c r="E32">
+        <f>IF('UC1'!E7="","",'UC1'!E7)</f>
+        <v>57</v>
+      </c>
+      <c r="G32" t="str">
+        <f>IF('UC1'!G7="","",'UC1'!G7)</f>
+        <v>HIGH_NO_REVIEW</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF('UC1'!A8="","",'UC1'!A8)</f>
+        <v>GL-0014</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF('UC1'!B8="","",'UC1'!B8)</f>
+        <v>Noah Harris</v>
+      </c>
+      <c r="C33" t="str">
+        <f>IF('UC1'!C8="","",'UC1'!C8)</f>
+        <v>Penrith GP Clinic</v>
+      </c>
+      <c r="D33" s="25">
+        <f>IF('UC1'!D8="","",'UC1'!D8)</f>
+        <v>46244</v>
+      </c>
+      <c r="E33">
+        <f>IF('UC1'!E8="","",'UC1'!E8)</f>
+        <v>58</v>
+      </c>
+      <c r="G33" t="str">
+        <f>IF('UC1'!G8="","",'UC1'!G8)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF('UC1'!A9="","",'UC1'!A9)</f>
+        <v>GL-0016</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF('UC1'!B9="","",'UC1'!B9)</f>
+        <v>Zoe Clark</v>
+      </c>
+      <c r="C34" t="str">
+        <f>IF('UC1'!C9="","",'UC1'!C9)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D34" s="25">
+        <f>IF('UC1'!D9="","",'UC1'!D9)</f>
+        <v>46178</v>
+      </c>
+      <c r="E34">
+        <f>IF('UC1'!E9="","",'UC1'!E9)</f>
+        <v>65</v>
+      </c>
+      <c r="G34" t="str">
+        <f>IF('UC1'!G9="","",'UC1'!G9)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>IF('UC1'!A10="","",'UC1'!A10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8167F2-A75A-8242-871F-F27DA342D96E}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="str" cm="1">
+        <f t="array" ref="A6:A16">_xlfn.SORTBY('UC2'!A2:A12&amp;" "&amp;'UC2'!B2:B12&amp;" ("&amp;TEXT('UC2'!G2:G12,"0.000")&amp;")", 'UC2'!G2:G12, 1)</f>
+        <v>GL-0002 Mei Chen (0.333)</v>
+      </c>
+      <c r="B6" cm="1">
+        <f t="array" ref="B6:B16">_xlfn._xlws.SORT('UC2'!G2:G12)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="C6" t="str" cm="1">
+        <f t="array" ref="C6:C16">_xlfn.SORTBY('UC2'!H2:H12, 'UC2'!G2:G12, 1)</f>
+        <v>NON_ADHERENT</v>
+      </c>
+      <c r="D6" t="e">
+        <f>IF(C6="ADHERENT", B6, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E6">
+        <f>IF(C6="NON_ADHERENT", B6, NA())</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="F6" t="str" cm="1">
+        <f t="array" ref="F6:F16">_xlfn.SORTBY('UC2'!C2:C12, 'UC2'!G2:G12, 1)</f>
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <v>GL-0010 William Jones (0.500)</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7" t="str">
+        <v>NON_ADHERENT</v>
+      </c>
+      <c r="D7" t="e">
+        <f>IF(C7="ADHERENT", B7, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7">
+        <f>IF(C7="NON_ADHERENT", B7, NA())</f>
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <v>GL-0017 Ethan Lewis (0.917)</v>
+      </c>
+      <c r="B8">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D8">
+        <f>IF(C8="ADHERENT", B8, NA())</f>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="E8" t="e">
+        <f>IF(C8="NON_ADHERENT", B8, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="str">
+        <v>GL-0005 James Wilson (0.972)</v>
+      </c>
+      <c r="B9">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D9">
+        <f>IF(C9="ADHERENT", B9, NA())</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="E9" t="e">
+        <f>IF(C9="NON_ADHERENT", B9, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F9" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
+        <v>GL-0012 Lucas Martin (0.972)</v>
+      </c>
+      <c r="B10">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D10">
+        <f>IF(C10="ADHERENT", B10, NA())</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="E10" t="e">
+        <f>IF(C10="NON_ADHERENT", B10, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <v>GL-0003 Ahmed Khan (0.978)</v>
+      </c>
+      <c r="B11">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:D16" si="0">IF(C11="ADHERENT", B11, NA())</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="E11" t="e">
+        <f t="shared" ref="E11:E16" si="1">IF(C11="NON_ADHERENT", B11, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <v>GL-0008 Sarah Lee (0.978)</v>
+      </c>
+      <c r="B12">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="E12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <v>GL-0001 Thomas Smith (0.989)</v>
+      </c>
+      <c r="B13">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E13" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <v>GL-0007 Daniel Nguyen (1.000)</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" t="str">
+        <v>sulfonylurea</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <v>GL-0009 Grace Taylor (1.000)</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <v>GL-0016 Zoe Clark (1.000)</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" t="str">
+        <v>DPP-4 inhibitor</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F16DFB2-8F2F-EA44-BB18-2E88CEFD301E}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="28"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="str">
+        <f>'UC3'!A2&amp;IF('UC3'!K2=TRUE," *","")&amp;IF('UC3'!I2="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0001 *</v>
+      </c>
+      <c r="B6" s="34">
+        <f>IF('UC3'!H2="","",'UC3'!H2)</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="35" t="str">
+        <f>'UC3'!I2</f>
+        <v>RISING</v>
+      </c>
+      <c r="D6" s="34">
+        <f>IF('UC3'!I2="RISING",'UC3'!H2,NA())</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="34" t="e">
+        <f>IF('UC3'!I2="STABLE",'UC3'!H2,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="35">
+        <f>'UC3'!C2</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="35">
+        <f>IF('UC3'!J2="","",'UC3'!J2)</f>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="H6" s="36" t="b">
+        <f>'UC3'!K2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="33" t="str">
+        <f>'UC3'!A3&amp;IF('UC3'!K3=TRUE," *","")&amp;IF('UC3'!I3="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0002</v>
+      </c>
+      <c r="B7" s="34">
+        <f>IF('UC3'!H3="","",'UC3'!H3)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="35" t="str">
+        <f>'UC3'!I3</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D7" s="34" t="e">
+        <f>IF('UC3'!I3="RISING",'UC3'!H3,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" s="34">
+        <f>IF('UC3'!I3="STABLE",'UC3'!H3,NA())</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="35">
+        <f>'UC3'!C3</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="35">
+        <f>IF('UC3'!J3="","",'UC3'!J3)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="H7" s="36" t="b">
+        <f>'UC3'!K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="33" t="str">
+        <f>'UC3'!A4&amp;IF('UC3'!K4=TRUE," *","")&amp;IF('UC3'!I4="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0003 (1 test)</v>
+      </c>
+      <c r="B8" s="34" t="str">
+        <f>IF('UC3'!H4="","",'UC3'!H4)</f>
+        <v/>
+      </c>
+      <c r="C8" s="35" t="str">
+        <f>'UC3'!I4</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D8" s="34" t="e">
+        <f>IF('UC3'!I4="RISING",'UC3'!H4,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="34" t="e">
+        <f>IF('UC3'!I4="STABLE",'UC3'!H4,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" s="35">
+        <f>'UC3'!C4</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="35">
+        <f>IF('UC3'!J4="","",'UC3'!J4)</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H8" s="36" t="b">
+        <f>'UC3'!K4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="33" t="str">
+        <f>'UC3'!A5&amp;IF('UC3'!K5=TRUE," *","")&amp;IF('UC3'!I5="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0004</v>
+      </c>
+      <c r="B9" s="34">
+        <f>IF('UC3'!H5="","",'UC3'!H5)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="35" t="str">
+        <f>'UC3'!I5</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D9" s="34" t="e">
+        <f>IF('UC3'!I5="RISING",'UC3'!H5,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" s="34">
+        <f>IF('UC3'!I5="STABLE",'UC3'!H5,NA())</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="35">
+        <f>'UC3'!C5</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="35" t="str">
+        <f>IF('UC3'!J5="","",'UC3'!J5)</f>
+        <v/>
+      </c>
+      <c r="H9" s="36" t="b">
+        <f>'UC3'!K5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="33" t="str">
+        <f>'UC3'!A6&amp;IF('UC3'!K6=TRUE," *","")&amp;IF('UC3'!I6="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0005</v>
+      </c>
+      <c r="B10" s="34">
+        <f>IF('UC3'!H6="","",'UC3'!H6)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C10" s="35" t="str">
+        <f>'UC3'!I6</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D10" s="34" t="e">
+        <f>IF('UC3'!I6="RISING",'UC3'!H6,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="34">
+        <f>IF('UC3'!I6="STABLE",'UC3'!H6,NA())</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F10" s="35">
+        <f>'UC3'!C6</f>
+        <v>2</v>
+      </c>
+      <c r="G10" s="35">
+        <f>IF('UC3'!J6="","",'UC3'!J6)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H10" s="36" t="b">
+        <f>'UC3'!K6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="33" t="str">
+        <f>'UC3'!A7&amp;IF('UC3'!K7=TRUE," *","")&amp;IF('UC3'!I7="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0007 (1 test)</v>
+      </c>
+      <c r="B11" s="34" t="str">
+        <f>IF('UC3'!H7="","",'UC3'!H7)</f>
+        <v/>
+      </c>
+      <c r="C11" s="35" t="str">
+        <f>'UC3'!I7</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D11" s="34" t="e">
+        <f>IF('UC3'!I7="RISING",'UC3'!H7,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="34" t="e">
+        <f>IF('UC3'!I7="STABLE",'UC3'!H7,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="35">
+        <f>'UC3'!C7</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="35">
+        <f>IF('UC3'!J7="","",'UC3'!J7)</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="36" t="b">
+        <f>'UC3'!K7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="str">
+        <f>'UC3'!A8&amp;IF('UC3'!K8=TRUE," *","")&amp;IF('UC3'!I8="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0008</v>
+      </c>
+      <c r="B12" s="34">
+        <f>IF('UC3'!H8="","",'UC3'!H8)</f>
+        <v>-1</v>
+      </c>
+      <c r="C12" s="35" t="str">
+        <f>'UC3'!I8</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D12" s="34" t="e">
+        <f>IF('UC3'!I8="RISING",'UC3'!H8,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="34">
+        <f>IF('UC3'!I8="STABLE",'UC3'!H8,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F12" s="35">
+        <f>'UC3'!C8</f>
+        <v>2</v>
+      </c>
+      <c r="G12" s="35">
+        <f>IF('UC3'!J8="","",'UC3'!J8)</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H12" s="36" t="b">
+        <f>'UC3'!K8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="str">
+        <f>'UC3'!A9&amp;IF('UC3'!K9=TRUE," *","")&amp;IF('UC3'!I9="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0009</v>
+      </c>
+      <c r="B13" s="34">
+        <f>IF('UC3'!H9="","",'UC3'!H9)</f>
+        <v>-1</v>
+      </c>
+      <c r="C13" s="35" t="str">
+        <f>'UC3'!I9</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D13" s="34" t="e">
+        <f>IF('UC3'!I9="RISING",'UC3'!H9,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="34">
+        <f>IF('UC3'!I9="STABLE",'UC3'!H9,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F13" s="35">
+        <f>'UC3'!C9</f>
+        <v>4</v>
+      </c>
+      <c r="G13" s="35">
+        <f>IF('UC3'!J9="","",'UC3'!J9)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="36" t="b">
+        <f>'UC3'!K9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="33" t="str">
+        <f>'UC3'!A10&amp;IF('UC3'!K10=TRUE," *","")&amp;IF('UC3'!I10="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0010 (1 test)</v>
+      </c>
+      <c r="B14" s="34" t="str">
+        <f>IF('UC3'!H10="","",'UC3'!H10)</f>
+        <v/>
+      </c>
+      <c r="C14" s="35" t="str">
+        <f>'UC3'!I10</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D14" s="34" t="e">
+        <f>IF('UC3'!I10="RISING",'UC3'!H10,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="34" t="e">
+        <f>IF('UC3'!I10="STABLE",'UC3'!H10,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="35">
+        <f>'UC3'!C10</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="35">
+        <f>IF('UC3'!J10="","",'UC3'!J10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="36" t="b">
+        <f>'UC3'!K10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="33" t="str">
+        <f>'UC3'!A11&amp;IF('UC3'!K11=TRUE," *","")&amp;IF('UC3'!I11="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0011</v>
+      </c>
+      <c r="B15" s="34">
+        <f>IF('UC3'!H11="","",'UC3'!H11)</f>
+        <v>-4</v>
+      </c>
+      <c r="C15" s="35" t="str">
+        <f>'UC3'!I11</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D15" s="34" t="e">
+        <f>IF('UC3'!I11="RISING",'UC3'!H11,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="34">
+        <f>IF('UC3'!I11="STABLE",'UC3'!H11,NA())</f>
+        <v>-4</v>
+      </c>
+      <c r="F15" s="35">
+        <f>'UC3'!C11</f>
+        <v>2</v>
+      </c>
+      <c r="G15" s="35" t="str">
+        <f>IF('UC3'!J11="","",'UC3'!J11)</f>
+        <v/>
+      </c>
+      <c r="H15" s="36" t="b">
+        <f>'UC3'!K11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="str">
+        <f>'UC3'!A12&amp;IF('UC3'!K12=TRUE," *","")&amp;IF('UC3'!I12="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0012 (1 test)</v>
+      </c>
+      <c r="B16" s="34" t="str">
+        <f>IF('UC3'!H12="","",'UC3'!H12)</f>
+        <v/>
+      </c>
+      <c r="C16" s="35" t="str">
+        <f>'UC3'!I12</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D16" s="34" t="e">
+        <f>IF('UC3'!I12="RISING",'UC3'!H12,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="34" t="e">
+        <f>IF('UC3'!I12="STABLE",'UC3'!H12,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="35">
+        <f>'UC3'!C12</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="35">
+        <f>IF('UC3'!J12="","",'UC3'!J12)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H16" s="36" t="b">
+        <f>'UC3'!K12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="33" t="str">
+        <f>'UC3'!A13&amp;IF('UC3'!K13=TRUE," *","")&amp;IF('UC3'!I13="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0013</v>
+      </c>
+      <c r="B17" s="34">
+        <f>IF('UC3'!H13="","",'UC3'!H13)</f>
+        <v>5</v>
+      </c>
+      <c r="C17" s="35" t="str">
+        <f>'UC3'!I13</f>
+        <v>RISING</v>
+      </c>
+      <c r="D17" s="34">
+        <f>IF('UC3'!I13="RISING",'UC3'!H13,NA())</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="34" t="e">
+        <f>IF('UC3'!I13="STABLE",'UC3'!H13,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="35">
+        <f>'UC3'!C13</f>
+        <v>2</v>
+      </c>
+      <c r="G17" s="35" t="str">
+        <f>IF('UC3'!J13="","",'UC3'!J13)</f>
+        <v/>
+      </c>
+      <c r="H17" s="36" t="b">
+        <f>'UC3'!K13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="str">
+        <f>'UC3'!A14&amp;IF('UC3'!K14=TRUE," *","")&amp;IF('UC3'!I14="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0014</v>
+      </c>
+      <c r="B18" s="34">
+        <f>IF('UC3'!H14="","",'UC3'!H14)</f>
+        <v>6</v>
+      </c>
+      <c r="C18" s="35" t="str">
+        <f>'UC3'!I14</f>
+        <v>RISING</v>
+      </c>
+      <c r="D18" s="34">
+        <f>IF('UC3'!I14="RISING",'UC3'!H14,NA())</f>
+        <v>6</v>
+      </c>
+      <c r="E18" s="34" t="e">
+        <f>IF('UC3'!I14="STABLE",'UC3'!H14,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="35">
+        <f>'UC3'!C14</f>
+        <v>2</v>
+      </c>
+      <c r="G18" s="35" t="str">
+        <f>IF('UC3'!J14="","",'UC3'!J14)</f>
+        <v/>
+      </c>
+      <c r="H18" s="36" t="b">
+        <f>'UC3'!K14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="str">
+        <f>'UC3'!A15&amp;IF('UC3'!K15=TRUE," *","")&amp;IF('UC3'!I15="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0015</v>
+      </c>
+      <c r="B19" s="34">
+        <f>IF('UC3'!H15="","",'UC3'!H15)</f>
+        <v>-1</v>
+      </c>
+      <c r="C19" s="35" t="str">
+        <f>'UC3'!I15</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D19" s="34" t="e">
+        <f>IF('UC3'!I15="RISING",'UC3'!H15,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="34">
+        <f>IF('UC3'!I15="STABLE",'UC3'!H15,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F19" s="35">
+        <f>'UC3'!C15</f>
+        <v>2</v>
+      </c>
+      <c r="G19" s="35" t="str">
+        <f>IF('UC3'!J15="","",'UC3'!J15)</f>
+        <v/>
+      </c>
+      <c r="H19" s="36" t="b">
+        <f>'UC3'!K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="33" t="str">
+        <f>'UC3'!A16&amp;IF('UC3'!K16=TRUE," *","")&amp;IF('UC3'!I16="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0016 *</v>
+      </c>
+      <c r="B20" s="34">
+        <f>IF('UC3'!H16="","",'UC3'!H16)</f>
+        <v>12</v>
+      </c>
+      <c r="C20" s="35" t="str">
+        <f>'UC3'!I16</f>
+        <v>RISING</v>
+      </c>
+      <c r="D20" s="34">
+        <f>IF('UC3'!I16="RISING",'UC3'!H16,NA())</f>
+        <v>12</v>
+      </c>
+      <c r="E20" s="34" t="e">
+        <f>IF('UC3'!I16="STABLE",'UC3'!H16,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="35">
+        <f>'UC3'!C16</f>
+        <v>2</v>
+      </c>
+      <c r="G20" s="35">
+        <f>IF('UC3'!J16="","",'UC3'!J16)</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="36" t="b">
+        <f>'UC3'!K16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="37" t="str">
+        <f>'UC3'!A17&amp;IF('UC3'!K17=TRUE," *","")&amp;IF('UC3'!I17="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0017 (1 test)</v>
+      </c>
+      <c r="B21" s="38" t="str">
+        <f>IF('UC3'!H17="","",'UC3'!H17)</f>
+        <v/>
+      </c>
+      <c r="C21" s="15" t="str">
+        <f>'UC3'!I17</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D21" s="38" t="e">
+        <f>IF('UC3'!I17="RISING",'UC3'!H17,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="38" t="e">
+        <f>IF('UC3'!I17="STABLE",'UC3'!H17,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="15">
+        <f>'UC3'!C17</f>
+        <v>1</v>
+      </c>
+      <c r="G21" s="15">
+        <f>IF('UC3'!J17="","",'UC3'!J17)</f>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="H21" s="39" t="b">
+        <f>'UC3'!K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34756B46-37E2-834C-9EF2-57F95F4F90C1}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="36">
+        <f>COUNTIF('UC4'!C:C,A6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="39">
+        <f>COUNTIF('UC4'!C:C,A7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8">
+        <f>SUM(B6:B7)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="33" t="str">
+        <f>IF('UC4'!A2="","",'UC4'!A2)</f>
+        <v>GL-0004</v>
+      </c>
+      <c r="B25" s="35" t="str">
+        <f>IF('UC4'!B2="","",'UC4'!B2)</f>
+        <v>Olivia Brown</v>
+      </c>
+      <c r="C25" s="35" t="str">
+        <f>IF('UC4'!C2="","",'UC4'!C2)</f>
+        <v>RESULT_NOT_RETURNED</v>
+      </c>
+      <c r="D25" s="45">
+        <f>IF('UC4'!E2="","",'UC4'!E2)</f>
+        <v>46087</v>
+      </c>
+      <c r="E25" s="46" t="str">
+        <f>IF('UC4'!D2="","",'UC4'!D2)</f>
+        <v>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</v>
+      </c>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="47"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="37" t="str">
+        <f>IF('UC4'!A3="","",'UC4'!A3)</f>
+        <v>GL-0005</v>
+      </c>
+      <c r="B26" s="15" t="str">
+        <f>IF('UC4'!B3="","",'UC4'!B3)</f>
+        <v>James Wilson</v>
+      </c>
+      <c r="C26" s="15" t="str">
+        <f>IF('UC4'!C3="","",'UC4'!C3)</f>
+        <v>MULTI_PHARMACY_OVERLAP</v>
+      </c>
+      <c r="D26" s="48">
+        <f>IF('UC4'!E3="","",'UC4'!E3)</f>
+        <v>46132</v>
+      </c>
+      <c r="E26" s="49" t="str">
+        <f>IF('UC4'!D3="","",'UC4'!D3)</f>
+        <v>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</v>
+      </c>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E25:J25"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E24:J24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1157,39 +8185,39 @@
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D2" s="4">
         <v>46162</v>
@@ -1198,10 +8226,10 @@
         <v>62</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H2" s="4">
         <v>46266</v>
@@ -1209,13 +8237,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D3" s="4">
         <v>46204</v>
@@ -1224,10 +8252,10 @@
         <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="H3" s="4">
         <v>46266</v>
@@ -1235,13 +8263,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D4" s="4">
         <v>45992</v>
@@ -1250,10 +8278,10 @@
         <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H4" s="4">
         <v>46266</v>
@@ -1261,25 +8289,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H5" s="4">
         <v>46266</v>
@@ -1287,13 +8315,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D6" s="4">
         <v>46054</v>
@@ -1302,10 +8330,10 @@
         <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H6" s="4">
         <v>46266</v>
@@ -1313,13 +8341,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4">
         <v>46152</v>
@@ -1328,10 +8356,10 @@
         <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H7" s="4">
         <v>46266</v>
@@ -1339,13 +8367,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D8" s="4">
         <v>46244</v>
@@ -1354,10 +8382,10 @@
         <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="H8" s="4">
         <v>46266</v>
@@ -1365,13 +8393,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4">
         <v>46178</v>
@@ -1380,10 +8408,10 @@
         <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="H9" s="4">
         <v>46266</v>
@@ -1395,7 +8423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1405,48 +8433,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D2" s="3">
         <v>7</v>
@@ -1461,7 +8489,7 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I2" s="4">
         <v>46086</v>
@@ -1475,13 +8503,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" s="3">
         <v>3</v>
@@ -1496,7 +8524,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I3" s="4">
         <v>46086</v>
@@ -1510,13 +8538,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" s="3">
         <v>6</v>
@@ -1531,7 +8559,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I4" s="4">
         <v>46086</v>
@@ -1545,13 +8573,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D5" s="3">
         <v>8</v>
@@ -1566,7 +8594,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I5" s="4">
         <v>46086</v>
@@ -1580,13 +8608,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -1601,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I6" s="4">
         <v>46086</v>
@@ -1615,13 +8643,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
@@ -1636,7 +8664,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I7" s="4">
         <v>46086</v>
@@ -1650,13 +8678,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
@@ -1671,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I8" s="4">
         <v>46086</v>
@@ -1685,13 +8713,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -1706,7 +8734,7 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I9" s="4">
         <v>46086</v>
@@ -1720,13 +8748,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3">
         <v>6</v>
@@ -1741,7 +8769,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I10" s="4">
         <v>46086</v>
@@ -1755,13 +8783,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="D11" s="3">
         <v>7</v>
@@ -1776,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="4">
         <v>46086</v>
@@ -1790,13 +8818,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" s="3">
         <v>6</v>
@@ -1811,7 +8839,7 @@
         <v>0.91700000000000004</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I12" s="4">
         <v>46086</v>
@@ -1827,729 +8855,4 @@
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="12" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="3">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4">
-        <v>45940</v>
-      </c>
-      <c r="E2" s="3">
-        <v>50</v>
-      </c>
-      <c r="F2" s="4">
-        <v>46162</v>
-      </c>
-      <c r="G2" s="3">
-        <v>62</v>
-      </c>
-      <c r="H2" s="3">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="K2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4">
-        <v>45981</v>
-      </c>
-      <c r="E3" s="3">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46204</v>
-      </c>
-      <c r="G3" s="3">
-        <v>58</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="K3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>45992</v>
-      </c>
-      <c r="E4" s="3">
-        <v>51</v>
-      </c>
-      <c r="F4" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G4" s="3">
-        <v>51</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="K4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4">
-        <v>45993</v>
-      </c>
-      <c r="E5" s="3">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46175</v>
-      </c>
-      <c r="G5" s="3">
-        <v>48</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46027</v>
-      </c>
-      <c r="E6" s="3">
-        <v>50.8</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46147</v>
-      </c>
-      <c r="G6" s="3">
-        <v>51.9</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.97199999999999998</v>
-      </c>
-      <c r="K6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>46157</v>
-      </c>
-      <c r="E7" s="3">
-        <v>47.5</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G7" s="3">
-        <v>47.5</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="3">
-        <v>51</v>
-      </c>
-      <c r="F8" s="4">
-        <v>46198</v>
-      </c>
-      <c r="G8" s="3">
-        <v>50</v>
-      </c>
-      <c r="H8" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="K8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="3">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
-        <v>45928</v>
-      </c>
-      <c r="E9" s="3">
-        <v>49</v>
-      </c>
-      <c r="F9" s="4">
-        <v>46201</v>
-      </c>
-      <c r="G9" s="3">
-        <v>48</v>
-      </c>
-      <c r="H9" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46054</v>
-      </c>
-      <c r="E10" s="3">
-        <v>52</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46054</v>
-      </c>
-      <c r="G10" s="3">
-        <v>52</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46096</v>
-      </c>
-      <c r="E11" s="3">
-        <v>54</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46193</v>
-      </c>
-      <c r="G11" s="3">
-        <v>50</v>
-      </c>
-      <c r="H11" s="3">
-        <v>-4</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>46152</v>
-      </c>
-      <c r="E12" s="3">
-        <v>57</v>
-      </c>
-      <c r="F12" s="4">
-        <v>46152</v>
-      </c>
-      <c r="G12" s="3">
-        <v>57</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.97199999999999998</v>
-      </c>
-      <c r="K12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2</v>
-      </c>
-      <c r="D13" s="4">
-        <v>45971</v>
-      </c>
-      <c r="E13" s="3">
-        <v>55</v>
-      </c>
-      <c r="F13" s="4">
-        <v>46122</v>
-      </c>
-      <c r="G13" s="3">
-        <v>60</v>
-      </c>
-      <c r="H13" s="3">
-        <v>5</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="4">
-        <v>46063</v>
-      </c>
-      <c r="E14" s="3">
-        <v>52</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46244</v>
-      </c>
-      <c r="G14" s="3">
-        <v>58</v>
-      </c>
-      <c r="H14" s="3">
-        <v>6</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="3">
-        <v>2</v>
-      </c>
-      <c r="D15" s="4">
-        <v>46113</v>
-      </c>
-      <c r="E15" s="3">
-        <v>51</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46204</v>
-      </c>
-      <c r="G15" s="3">
-        <v>50</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="3">
-        <v>2</v>
-      </c>
-      <c r="D16" s="4">
-        <v>45966</v>
-      </c>
-      <c r="E16" s="3">
-        <v>53</v>
-      </c>
-      <c r="F16" s="4">
-        <v>46178</v>
-      </c>
-      <c r="G16" s="3">
-        <v>65</v>
-      </c>
-      <c r="H16" s="3">
-        <v>12</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="3">
-        <v>1</v>
-      </c>
-      <c r="K16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
-        <v>46137</v>
-      </c>
-      <c r="E17" s="3">
-        <v>49</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46137</v>
-      </c>
-      <c r="G17" s="3">
-        <v>49</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="K17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>46266</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="5" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="6">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
+++ b/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
@@ -5,44 +5,83 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Project/glucolink-a2/docs/excel_reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEDADE2-76F4-5244-82FE-320AB97A2928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BAC49-4570-CC41-83F3-D51EA4CB1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="680" windowWidth="24120" windowHeight="19960" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="20160" windowHeight="19280" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
     <sheet name="Checks" sheetId="2" r:id="rId2"/>
     <sheet name="Queries" sheetId="3" r:id="rId3"/>
-    <sheet name="UC1" sheetId="4" r:id="rId4"/>
-    <sheet name="UC2" sheetId="5" r:id="rId5"/>
-    <sheet name="UC3" sheetId="6" r:id="rId6"/>
-    <sheet name="UC4" sheetId="7" r:id="rId7"/>
+    <sheet name="UC1 Dashboard" sheetId="8" r:id="rId4"/>
+    <sheet name="UC2 Dashboard" sheetId="9" r:id="rId5"/>
+    <sheet name="UC3 Dashboard" sheetId="10" r:id="rId6"/>
+    <sheet name="UC4 Dashboard" sheetId="11" r:id="rId7"/>
+    <sheet name="UC1" sheetId="4" r:id="rId8"/>
+    <sheet name="UC2" sheetId="5" r:id="rId9"/>
+    <sheet name="UC3" sheetId="6" r:id="rId10"/>
+    <sheet name="UC4" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UC1'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'UC2'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'UC3'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'UC4'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'UC1'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'UC2'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'UC3'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UC4'!$A$1:$E$1</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'UC1 Dashboard'!$B$5</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'UC1 Dashboard'!$B$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="104">
-  <si>
-    <t>GlucoLink reporting export — template</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="163">
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>NOT LOADED — no reporting data included</t>
-  </si>
-  <si>
     <t>Database</t>
   </si>
   <si>
@@ -97,9 +136,6 @@
     <t>UC1 rows</t>
   </si>
   <si>
-    <t>NOT RUN</t>
-  </si>
-  <si>
     <t>UC2 rows</t>
   </si>
   <si>
@@ -262,9 +298,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>UC2 rows 11, NON_ADHERENT 2; ADHERENT 9</t>
-  </si>
-  <si>
     <t>GL-0001</t>
   </si>
   <si>
@@ -344,16 +377,207 @@
   </si>
   <si>
     <t>Ethan Lewis</t>
+  </si>
+  <si>
+    <t>Parramatta Family Practice</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>HIGH_NO_REVIEW</t>
+  </si>
+  <si>
+    <t>HIGH_REVIEW_PENDING</t>
+  </si>
+  <si>
+    <t>Blacktown Medical Centre</t>
+  </si>
+  <si>
+    <t>OVERDUE_TEST</t>
+  </si>
+  <si>
+    <t>GL-0006</t>
+  </si>
+  <si>
+    <t>NO_TEST_ON_RECORD</t>
+  </si>
+  <si>
+    <t>GL-0014</t>
+  </si>
+  <si>
+    <t>Noah Harris</t>
+  </si>
+  <si>
+    <t>Penrith GP Clinic</t>
+  </si>
+  <si>
+    <t>RISING</t>
+  </si>
+  <si>
+    <t>STABLE</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_HISTORY</t>
+  </si>
+  <si>
+    <t>GL-0004</t>
+  </si>
+  <si>
+    <t>Olivia Brown</t>
+  </si>
+  <si>
+    <t>GL-0011</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>GL-0013</t>
+  </si>
+  <si>
+    <t>Chloe White</t>
+  </si>
+  <si>
+    <t>GL-0015</t>
+  </si>
+  <si>
+    <t>Ava Robinson</t>
+  </si>
+  <si>
+    <t>RESULT_NOT_RETURNED</t>
+  </si>
+  <si>
+    <t>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</t>
+  </si>
+  <si>
+    <t>MULTI_PHARMACY_OVERLAP</t>
+  </si>
+  <si>
+    <t>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</t>
+  </si>
+  <si>
+    <t>LOADED: all four views from one read-only snapshot of the frozen database</t>
+  </si>
+  <si>
+    <t>glucolink_a2 (shared PostgreSQL 15.19 server, CloudBeaver connection 'GlucoLink A2 - Team')</t>
+  </si>
+  <si>
+    <t>9a499ce (frozen SQL 00 to 09; shared DB rebuilt from it on 11 Oct 2026)</t>
+  </si>
+  <si>
+    <t>2026-10-14 17:12 ; all four views in the same session</t>
+  </si>
+  <si>
+    <t>Read-only SELECT statements from the Queries sheet, run through CloudBeaver on glucolink_a2. Consistent snapshot: yes. The database is frozen (SELECT only) since the 11 Oct rebuild.</t>
+  </si>
+  <si>
+    <t>Minha Kim, 2026-10-14</t>
+  </si>
+  <si>
+    <t>GlucoLink reporting export</t>
+  </si>
+  <si>
+    <t>Rule parameters (actual, reporting.rule_parameter)</t>
+  </si>
+  <si>
+    <t>param_name</t>
+  </si>
+  <si>
+    <t>param_value</t>
+  </si>
+  <si>
+    <t>2026_09_01</t>
+  </si>
+  <si>
+    <t>hba1c_high_mmol</t>
+  </si>
+  <si>
+    <t>pdc_threshold</t>
+  </si>
+  <si>
+    <t>pdc_window_days</t>
+  </si>
+  <si>
+    <t>return_grace_days</t>
+  </si>
+  <si>
+    <t>review_window_days</t>
+  </si>
+  <si>
+    <t>test_overdue_months</t>
+  </si>
+  <si>
+    <t>trend_min_change_mmol</t>
+  </si>
+  <si>
+    <t>trend_window_months</t>
+  </si>
+  <si>
+    <t>Automated tests (audit.test_results)</t>
+  </si>
+  <si>
+    <t>46 run, 46 passed, 0 failed</t>
+  </si>
+  <si>
+    <t>UC1 Care gaps: patient per care-gap status</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_uc1_care_gaps | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
+  </si>
+  <si>
+    <t>patients</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>UC2 Medication adherence: PDC per patient (threshold 0.8)</t>
+  </si>
+  <si>
+    <t>patient (sorted by PDC)</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_uc2_pdc | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
+  </si>
+  <si>
+    <t>UC3 HbA1c trend: change in HbA1c per patient</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>Practice nurse: book an HbA1c test for overdue or untested patients, and a GP review for high results with no review.</t>
+  </si>
+  <si>
+    <t>Community pharmacist: contact NON_ADHERENT patients (PDC below 0.8) about refills and barriers to taking their medication.</t>
+  </si>
+  <si>
+    <t>GP: review treatment for RISING patients; * = rising despite adherence, so consider a change of therapy rather than an adherence talk.</t>
+  </si>
+  <si>
+    <t>INSUFFICIENT_HISTORY (fewer than 2 tests) has no change value, so it has no bar; it is not drawn as zero. FALLING: 0 patients.</t>
+  </si>
+  <si>
+    <t>UC4 Care-path breaks: breaks per type</t>
+  </si>
+  <si>
+    <t>GlucoLink network care coordinator: ask the lab to resend the missing result to the clinic, and contact the patient and both pharmacies about the overlapping supply.</t>
+  </si>
+  <si>
+    <t>breaks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="171" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="173" formatCode="\+0.00;\-0.00;0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,8 +596,43 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20334C"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -385,8 +644,14 @@
         <fgColor rgb="FF19334D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -409,11 +674,181 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -423,6 +858,88 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,6 +955,4258 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>patients per care-gap status (n = 8)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC1 Dashboard'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>patients</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="2.5856129685916919E-2"/>
+                      <c:h val="3.4435066335886097E-2"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC1 Dashboard'!$A$6:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>HIGH_NO_REVIEW</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HIGH_REVIEW_PENDING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>OVERDUE_TEST</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>NO_TEST_ON_RECORD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC1 Dashboard'!$B$6:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-08FA-CE4F-9AF0-12F80AEAF8DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1564980800"/>
+        <c:axId val="1564982144"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1564980800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564982144"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1564982144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564980800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>PDC</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>per. atient,</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>lowest</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
+              <a:t>first</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-AU" altLang="ko-KR" baseline="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADHERENT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$A$6:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>GL-0002 Mei Chen (0.333)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0010 William Jones (0.500)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0017 Ethan Lewis (0.917)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0005 James Wilson (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0012 Lucas Martin (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0003 Ahmed Khan (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008 Sarah Lee (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0001 Thomas Smith (0.989)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0007 Daniel Nguyen (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0009 Grace Taylor (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0016 Zoe Clark (1.000)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC2 Dashboard'!$D$6:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.98899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E39B-5D49-B21B-4ABC7832F6BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NON_ADHERENT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC2 Dashboard'!$A$6:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>GL-0002 Mei Chen (0.333)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0010 William Jones (0.500)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0017 Ethan Lewis (0.917)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0005 James Wilson (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0012 Lucas Martin (0.972)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0003 Ahmed Khan (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008 Sarah Lee (0.978)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0001 Thomas Smith (0.989)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0007 Daniel Nguyen (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0009 Grace Taylor (1.000)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0016 Zoe Clark (1.000)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC2 Dashboard'!$E$6:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.33300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E39B-5D49-B21B-4ABC7832F6BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="40"/>
+        <c:overlap val="100"/>
+        <c:axId val="1647495808"/>
+        <c:axId val="1647498496"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1647495808"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1647498496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1647498496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1647495808"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-AU" sz="1800">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>HbA1c change from first to last test (mmol/mol) </a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-AU" sz="1800">
+                <a:effectLst/>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-AU" sz="1000">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>* = rising despite adherence</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-AU" sz="1800">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RISING</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$A$6:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>GL-0001 *</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0003 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0007 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0010 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0011</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0012 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>GL-0013</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>GL-0014</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>GL-0015</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>GL-0016 *</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>GL-0017 (1 test)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC3 Dashboard'!$D$6:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>\+0.00;\-0.00;0</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-46CD-AF41-96F6-6302E5C7632C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>STABLE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC3 Dashboard'!$A$6:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>GL-0001 *</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>GL-0002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GL-0003 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GL-0004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GL-0005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GL-0007 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>GL-0008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>GL-0009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>GL-0010 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>GL-0011</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>GL-0012 (1 test)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>GL-0013</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>GL-0014</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>GL-0015</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>GL-0016 *</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>GL-0017 (1 test)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC3 Dashboard'!$E$6:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>\+0.00;\-0.00;0</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-46CD-AF41-96F6-6302E5C7632C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="50"/>
+        <c:overlap val="100"/>
+        <c:axId val="1564609600"/>
+        <c:axId val="1564621248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1564609600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564621248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1564621248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\+0.00;\-0.00;0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1564609600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Care-path</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> breaks per type (n = 2)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'UC4 Dashboard'!$A$6:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>RESULT_NOT_RETURNED</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MULTI_PHARMACY_OVERLAP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'UC4 Dashboard'!$B$6:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DA3B-4B43-A83E-629B9770251D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1592126400"/>
+        <c:axId val="1592123712"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1592126400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592123712"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1592123712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592126400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC75E2A0-F94B-714A-ADDA-81BEB6C4925D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CC09AC4-8487-83F7-0042-2313374AB9C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C052620-A1BC-7C3A-DA80-C34BAF1440A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02BB58DA-F14D-5A7C-0E3C-914F20845540}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -725,7 +5494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -734,79 +5503,910 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46266</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45940</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46162</v>
+      </c>
+      <c r="G2" s="3">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="K2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45981</v>
+      </c>
+      <c r="E3" s="3">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G3" s="3">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E4" s="3">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G4" s="3">
+        <v>51</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>45993</v>
+      </c>
+      <c r="E5" s="3">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G5" s="3">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46027</v>
+      </c>
+      <c r="E6" s="3">
+        <v>50.8</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46147</v>
+      </c>
+      <c r="G6" s="3">
+        <v>51.9</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="E7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G7" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="3">
+        <v>51</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46198</v>
+      </c>
+      <c r="G8" s="3">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <v>45928</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46201</v>
+      </c>
+      <c r="G9" s="3">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46054</v>
+      </c>
+      <c r="G10" s="3">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46096</v>
+      </c>
+      <c r="E11" s="3">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46193</v>
+      </c>
+      <c r="G11" s="3">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-4</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46152</v>
+      </c>
+      <c r="G12" s="3">
+        <v>57</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="K12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>45971</v>
+      </c>
+      <c r="E13" s="3">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G13" s="3">
+        <v>60</v>
+      </c>
+      <c r="H13" s="3">
+        <v>5</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46063</v>
+      </c>
+      <c r="E14" s="3">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46244</v>
+      </c>
+      <c r="G14" s="3">
+        <v>58</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G15" s="3">
+        <v>50</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45966</v>
+      </c>
+      <c r="E16" s="3">
+        <v>53</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46178</v>
+      </c>
+      <c r="G16" s="3">
+        <v>65</v>
+      </c>
+      <c r="H16" s="3">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="3">
+        <v>49</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G17" s="3">
+        <v>49</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="K17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46132</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -824,7 +6424,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -832,7 +6432,7 @@
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -840,150 +6440,170 @@
     </row>
     <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>19</v>
+      </c>
+      <c r="B5" s="2">
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
         <v>16</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2">
+        <v>16</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="D14" s="2" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1002,42 +6622,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1046,8 +6666,1518 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A92C5B-52A4-FE4D-B226-05D025B6D1B7}">
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="21">
+        <f>SUM(B6:B9)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>IF('UC1'!A2="","",'UC1'!A2)</f>
+        <v>GL-0001</v>
+      </c>
+      <c r="B27" t="str">
+        <f>IF('UC1'!B2="","",'UC1'!B2)</f>
+        <v>Thomas Smith</v>
+      </c>
+      <c r="C27" t="str">
+        <f>IF('UC1'!C2="","",'UC1'!C2)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D27" s="25">
+        <f>IF('UC1'!D2="","",'UC1'!D2)</f>
+        <v>46162</v>
+      </c>
+      <c r="E27">
+        <f>IF('UC1'!E2="","",'UC1'!E2)</f>
+        <v>62</v>
+      </c>
+      <c r="F27" t="str">
+        <f>IF('UC1'!F2="","",'UC1'!F2)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF('UC1'!G2="","",'UC1'!G2)</f>
+        <v>HIGH_NO_REVIEW</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>IF('UC1'!A3="","",'UC1'!A3)</f>
+        <v>GL-0002</v>
+      </c>
+      <c r="B28" t="str">
+        <f>IF('UC1'!B3="","",'UC1'!B3)</f>
+        <v>Mei Chen</v>
+      </c>
+      <c r="C28" t="str">
+        <f>IF('UC1'!C3="","",'UC1'!C3)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D28" s="25">
+        <f>IF('UC1'!D3="","",'UC1'!D3)</f>
+        <v>46204</v>
+      </c>
+      <c r="E28">
+        <f>IF('UC1'!E3="","",'UC1'!E3)</f>
+        <v>58</v>
+      </c>
+      <c r="G28" t="str">
+        <f>IF('UC1'!G3="","",'UC1'!G3)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>IF('UC1'!A4="","",'UC1'!A4)</f>
+        <v>GL-0003</v>
+      </c>
+      <c r="B29" t="str">
+        <f>IF('UC1'!B4="","",'UC1'!B4)</f>
+        <v>Ahmed Khan</v>
+      </c>
+      <c r="C29" t="str">
+        <f>IF('UC1'!C4="","",'UC1'!C4)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D29" s="25">
+        <f>IF('UC1'!D4="","",'UC1'!D4)</f>
+        <v>45992</v>
+      </c>
+      <c r="E29">
+        <f>IF('UC1'!E4="","",'UC1'!E4)</f>
+        <v>51</v>
+      </c>
+      <c r="G29" t="str">
+        <f>IF('UC1'!G4="","",'UC1'!G4)</f>
+        <v>OVERDUE_TEST</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
+        <f>IF('UC1'!A5="","",'UC1'!A5)</f>
+        <v>GL-0006</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF('UC1'!B5="","",'UC1'!B5)</f>
+        <v>Daniel Nguyen</v>
+      </c>
+      <c r="C30" t="str">
+        <f>IF('UC1'!C5="","",'UC1'!C5)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D30" s="25" t="str">
+        <f>IF('UC1'!D5="","",'UC1'!D5)</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF('UC1'!E5="","",'UC1'!E5)</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>IF('UC1'!G5="","",'UC1'!G5)</f>
+        <v>NO_TEST_ON_RECORD</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
+        <f>IF('UC1'!A6="","",'UC1'!A6)</f>
+        <v>GL-0010</v>
+      </c>
+      <c r="B31" t="str">
+        <f>IF('UC1'!B6="","",'UC1'!B6)</f>
+        <v>William Jones</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF('UC1'!C6="","",'UC1'!C6)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D31" s="25">
+        <f>IF('UC1'!D6="","",'UC1'!D6)</f>
+        <v>46054</v>
+      </c>
+      <c r="E31">
+        <f>IF('UC1'!E6="","",'UC1'!E6)</f>
+        <v>52</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IF('UC1'!G6="","",'UC1'!G6)</f>
+        <v>OVERDUE_TEST</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>IF('UC1'!A7="","",'UC1'!A7)</f>
+        <v>GL-0012</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF('UC1'!B7="","",'UC1'!B7)</f>
+        <v>Lucas Martin</v>
+      </c>
+      <c r="C32" t="str">
+        <f>IF('UC1'!C7="","",'UC1'!C7)</f>
+        <v>Parramatta Family Practice</v>
+      </c>
+      <c r="D32" s="25">
+        <f>IF('UC1'!D7="","",'UC1'!D7)</f>
+        <v>46152</v>
+      </c>
+      <c r="E32">
+        <f>IF('UC1'!E7="","",'UC1'!E7)</f>
+        <v>57</v>
+      </c>
+      <c r="G32" t="str">
+        <f>IF('UC1'!G7="","",'UC1'!G7)</f>
+        <v>HIGH_NO_REVIEW</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>IF('UC1'!A8="","",'UC1'!A8)</f>
+        <v>GL-0014</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF('UC1'!B8="","",'UC1'!B8)</f>
+        <v>Noah Harris</v>
+      </c>
+      <c r="C33" t="str">
+        <f>IF('UC1'!C8="","",'UC1'!C8)</f>
+        <v>Penrith GP Clinic</v>
+      </c>
+      <c r="D33" s="25">
+        <f>IF('UC1'!D8="","",'UC1'!D8)</f>
+        <v>46244</v>
+      </c>
+      <c r="E33">
+        <f>IF('UC1'!E8="","",'UC1'!E8)</f>
+        <v>58</v>
+      </c>
+      <c r="G33" t="str">
+        <f>IF('UC1'!G8="","",'UC1'!G8)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>IF('UC1'!A9="","",'UC1'!A9)</f>
+        <v>GL-0016</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF('UC1'!B9="","",'UC1'!B9)</f>
+        <v>Zoe Clark</v>
+      </c>
+      <c r="C34" t="str">
+        <f>IF('UC1'!C9="","",'UC1'!C9)</f>
+        <v>Blacktown Medical Centre</v>
+      </c>
+      <c r="D34" s="25">
+        <f>IF('UC1'!D9="","",'UC1'!D9)</f>
+        <v>46178</v>
+      </c>
+      <c r="E34">
+        <f>IF('UC1'!E9="","",'UC1'!E9)</f>
+        <v>65</v>
+      </c>
+      <c r="G34" t="str">
+        <f>IF('UC1'!G9="","",'UC1'!G9)</f>
+        <v>HIGH_REVIEW_PENDING</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>IF('UC1'!A10="","",'UC1'!A10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8167F2-A75A-8242-871F-F27DA342D96E}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="str" cm="1">
+        <f t="array" ref="A6:A16">_xlfn.SORTBY('UC2'!A2:A12&amp;" "&amp;'UC2'!B2:B12&amp;" ("&amp;TEXT('UC2'!G2:G12,"0.000")&amp;")", 'UC2'!G2:G12, 1)</f>
+        <v>GL-0002 Mei Chen (0.333)</v>
+      </c>
+      <c r="B6" cm="1">
+        <f t="array" ref="B6:B16">_xlfn._xlws.SORT('UC2'!G2:G12)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="C6" t="str" cm="1">
+        <f t="array" ref="C6:C16">_xlfn.SORTBY('UC2'!H2:H12, 'UC2'!G2:G12, 1)</f>
+        <v>NON_ADHERENT</v>
+      </c>
+      <c r="D6" t="e">
+        <f>IF(C6="ADHERENT", B6, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E6">
+        <f>IF(C6="NON_ADHERENT", B6, NA())</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="F6" t="str" cm="1">
+        <f t="array" ref="F6:F16">_xlfn.SORTBY('UC2'!C2:C12, 'UC2'!G2:G12, 1)</f>
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <v>GL-0010 William Jones (0.500)</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7" t="str">
+        <v>NON_ADHERENT</v>
+      </c>
+      <c r="D7" t="e">
+        <f>IF(C7="ADHERENT", B7, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7">
+        <f>IF(C7="NON_ADHERENT", B7, NA())</f>
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <v>GL-0017 Ethan Lewis (0.917)</v>
+      </c>
+      <c r="B8">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D8">
+        <f>IF(C8="ADHERENT", B8, NA())</f>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="E8" t="e">
+        <f>IF(C8="NON_ADHERENT", B8, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="str">
+        <v>GL-0005 James Wilson (0.972)</v>
+      </c>
+      <c r="B9">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D9">
+        <f>IF(C9="ADHERENT", B9, NA())</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="E9" t="e">
+        <f>IF(C9="NON_ADHERENT", B9, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F9" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
+        <v>GL-0012 Lucas Martin (0.972)</v>
+      </c>
+      <c r="B10">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D10">
+        <f>IF(C10="ADHERENT", B10, NA())</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="E10" t="e">
+        <f>IF(C10="NON_ADHERENT", B10, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <v>GL-0003 Ahmed Khan (0.978)</v>
+      </c>
+      <c r="B11">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:D16" si="0">IF(C11="ADHERENT", B11, NA())</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="E11" t="e">
+        <f t="shared" ref="E11:E16" si="1">IF(C11="NON_ADHERENT", B11, NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <v>GL-0008 Sarah Lee (0.978)</v>
+      </c>
+      <c r="B12">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="E12" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <v>GL-0001 Thomas Smith (0.989)</v>
+      </c>
+      <c r="B13">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E13" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <v>GL-0007 Daniel Nguyen (1.000)</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" t="str">
+        <v>sulfonylurea</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <v>GL-0009 Grace Taylor (1.000)</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" t="str">
+        <v>biguanide</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
+        <v>GL-0016 Zoe Clark (1.000)</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ADHERENT</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" t="str">
+        <v>DPP-4 inhibitor</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F16DFB2-8F2F-EA44-BB18-2E88CEFD301E}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="28"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="str">
+        <f>'UC3'!A2&amp;IF('UC3'!K2=TRUE," *","")&amp;IF('UC3'!I2="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0001 *</v>
+      </c>
+      <c r="B6" s="34">
+        <f>IF('UC3'!H2="","",'UC3'!H2)</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="35" t="str">
+        <f>'UC3'!I2</f>
+        <v>RISING</v>
+      </c>
+      <c r="D6" s="34">
+        <f>IF('UC3'!I2="RISING",'UC3'!H2,NA())</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="34" t="e">
+        <f>IF('UC3'!I2="STABLE",'UC3'!H2,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="35">
+        <f>'UC3'!C2</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="35">
+        <f>IF('UC3'!J2="","",'UC3'!J2)</f>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="H6" s="36" t="b">
+        <f>'UC3'!K2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="33" t="str">
+        <f>'UC3'!A3&amp;IF('UC3'!K3=TRUE," *","")&amp;IF('UC3'!I3="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0002</v>
+      </c>
+      <c r="B7" s="34">
+        <f>IF('UC3'!H3="","",'UC3'!H3)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="35" t="str">
+        <f>'UC3'!I3</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D7" s="34" t="e">
+        <f>IF('UC3'!I3="RISING",'UC3'!H3,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" s="34">
+        <f>IF('UC3'!I3="STABLE",'UC3'!H3,NA())</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="35">
+        <f>'UC3'!C3</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="35">
+        <f>IF('UC3'!J3="","",'UC3'!J3)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="H7" s="36" t="b">
+        <f>'UC3'!K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="33" t="str">
+        <f>'UC3'!A4&amp;IF('UC3'!K4=TRUE," *","")&amp;IF('UC3'!I4="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0003 (1 test)</v>
+      </c>
+      <c r="B8" s="34" t="str">
+        <f>IF('UC3'!H4="","",'UC3'!H4)</f>
+        <v/>
+      </c>
+      <c r="C8" s="35" t="str">
+        <f>'UC3'!I4</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D8" s="34" t="e">
+        <f>IF('UC3'!I4="RISING",'UC3'!H4,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="34" t="e">
+        <f>IF('UC3'!I4="STABLE",'UC3'!H4,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" s="35">
+        <f>'UC3'!C4</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="35">
+        <f>IF('UC3'!J4="","",'UC3'!J4)</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H8" s="36" t="b">
+        <f>'UC3'!K4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="33" t="str">
+        <f>'UC3'!A5&amp;IF('UC3'!K5=TRUE," *","")&amp;IF('UC3'!I5="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0004</v>
+      </c>
+      <c r="B9" s="34">
+        <f>IF('UC3'!H5="","",'UC3'!H5)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="35" t="str">
+        <f>'UC3'!I5</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D9" s="34" t="e">
+        <f>IF('UC3'!I5="RISING",'UC3'!H5,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" s="34">
+        <f>IF('UC3'!I5="STABLE",'UC3'!H5,NA())</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="35">
+        <f>'UC3'!C5</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="35" t="str">
+        <f>IF('UC3'!J5="","",'UC3'!J5)</f>
+        <v/>
+      </c>
+      <c r="H9" s="36" t="b">
+        <f>'UC3'!K5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="33" t="str">
+        <f>'UC3'!A6&amp;IF('UC3'!K6=TRUE," *","")&amp;IF('UC3'!I6="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0005</v>
+      </c>
+      <c r="B10" s="34">
+        <f>IF('UC3'!H6="","",'UC3'!H6)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C10" s="35" t="str">
+        <f>'UC3'!I6</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D10" s="34" t="e">
+        <f>IF('UC3'!I6="RISING",'UC3'!H6,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="34">
+        <f>IF('UC3'!I6="STABLE",'UC3'!H6,NA())</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F10" s="35">
+        <f>'UC3'!C6</f>
+        <v>2</v>
+      </c>
+      <c r="G10" s="35">
+        <f>IF('UC3'!J6="","",'UC3'!J6)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H10" s="36" t="b">
+        <f>'UC3'!K6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="33" t="str">
+        <f>'UC3'!A7&amp;IF('UC3'!K7=TRUE," *","")&amp;IF('UC3'!I7="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0007 (1 test)</v>
+      </c>
+      <c r="B11" s="34" t="str">
+        <f>IF('UC3'!H7="","",'UC3'!H7)</f>
+        <v/>
+      </c>
+      <c r="C11" s="35" t="str">
+        <f>'UC3'!I7</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D11" s="34" t="e">
+        <f>IF('UC3'!I7="RISING",'UC3'!H7,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="34" t="e">
+        <f>IF('UC3'!I7="STABLE",'UC3'!H7,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="35">
+        <f>'UC3'!C7</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="35">
+        <f>IF('UC3'!J7="","",'UC3'!J7)</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="36" t="b">
+        <f>'UC3'!K7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="str">
+        <f>'UC3'!A8&amp;IF('UC3'!K8=TRUE," *","")&amp;IF('UC3'!I8="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0008</v>
+      </c>
+      <c r="B12" s="34">
+        <f>IF('UC3'!H8="","",'UC3'!H8)</f>
+        <v>-1</v>
+      </c>
+      <c r="C12" s="35" t="str">
+        <f>'UC3'!I8</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D12" s="34" t="e">
+        <f>IF('UC3'!I8="RISING",'UC3'!H8,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="34">
+        <f>IF('UC3'!I8="STABLE",'UC3'!H8,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F12" s="35">
+        <f>'UC3'!C8</f>
+        <v>2</v>
+      </c>
+      <c r="G12" s="35">
+        <f>IF('UC3'!J8="","",'UC3'!J8)</f>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H12" s="36" t="b">
+        <f>'UC3'!K8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="str">
+        <f>'UC3'!A9&amp;IF('UC3'!K9=TRUE," *","")&amp;IF('UC3'!I9="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0009</v>
+      </c>
+      <c r="B13" s="34">
+        <f>IF('UC3'!H9="","",'UC3'!H9)</f>
+        <v>-1</v>
+      </c>
+      <c r="C13" s="35" t="str">
+        <f>'UC3'!I9</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D13" s="34" t="e">
+        <f>IF('UC3'!I9="RISING",'UC3'!H9,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="34">
+        <f>IF('UC3'!I9="STABLE",'UC3'!H9,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F13" s="35">
+        <f>'UC3'!C9</f>
+        <v>4</v>
+      </c>
+      <c r="G13" s="35">
+        <f>IF('UC3'!J9="","",'UC3'!J9)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="36" t="b">
+        <f>'UC3'!K9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="33" t="str">
+        <f>'UC3'!A10&amp;IF('UC3'!K10=TRUE," *","")&amp;IF('UC3'!I10="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0010 (1 test)</v>
+      </c>
+      <c r="B14" s="34" t="str">
+        <f>IF('UC3'!H10="","",'UC3'!H10)</f>
+        <v/>
+      </c>
+      <c r="C14" s="35" t="str">
+        <f>'UC3'!I10</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D14" s="34" t="e">
+        <f>IF('UC3'!I10="RISING",'UC3'!H10,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="34" t="e">
+        <f>IF('UC3'!I10="STABLE",'UC3'!H10,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="35">
+        <f>'UC3'!C10</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="35">
+        <f>IF('UC3'!J10="","",'UC3'!J10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="36" t="b">
+        <f>'UC3'!K10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="33" t="str">
+        <f>'UC3'!A11&amp;IF('UC3'!K11=TRUE," *","")&amp;IF('UC3'!I11="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0011</v>
+      </c>
+      <c r="B15" s="34">
+        <f>IF('UC3'!H11="","",'UC3'!H11)</f>
+        <v>-4</v>
+      </c>
+      <c r="C15" s="35" t="str">
+        <f>'UC3'!I11</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D15" s="34" t="e">
+        <f>IF('UC3'!I11="RISING",'UC3'!H11,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="34">
+        <f>IF('UC3'!I11="STABLE",'UC3'!H11,NA())</f>
+        <v>-4</v>
+      </c>
+      <c r="F15" s="35">
+        <f>'UC3'!C11</f>
+        <v>2</v>
+      </c>
+      <c r="G15" s="35" t="str">
+        <f>IF('UC3'!J11="","",'UC3'!J11)</f>
+        <v/>
+      </c>
+      <c r="H15" s="36" t="b">
+        <f>'UC3'!K11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="str">
+        <f>'UC3'!A12&amp;IF('UC3'!K12=TRUE," *","")&amp;IF('UC3'!I12="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0012 (1 test)</v>
+      </c>
+      <c r="B16" s="34" t="str">
+        <f>IF('UC3'!H12="","",'UC3'!H12)</f>
+        <v/>
+      </c>
+      <c r="C16" s="35" t="str">
+        <f>'UC3'!I12</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D16" s="34" t="e">
+        <f>IF('UC3'!I12="RISING",'UC3'!H12,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="34" t="e">
+        <f>IF('UC3'!I12="STABLE",'UC3'!H12,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="35">
+        <f>'UC3'!C12</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="35">
+        <f>IF('UC3'!J12="","",'UC3'!J12)</f>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H16" s="36" t="b">
+        <f>'UC3'!K12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="33" t="str">
+        <f>'UC3'!A13&amp;IF('UC3'!K13=TRUE," *","")&amp;IF('UC3'!I13="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0013</v>
+      </c>
+      <c r="B17" s="34">
+        <f>IF('UC3'!H13="","",'UC3'!H13)</f>
+        <v>5</v>
+      </c>
+      <c r="C17" s="35" t="str">
+        <f>'UC3'!I13</f>
+        <v>RISING</v>
+      </c>
+      <c r="D17" s="34">
+        <f>IF('UC3'!I13="RISING",'UC3'!H13,NA())</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="34" t="e">
+        <f>IF('UC3'!I13="STABLE",'UC3'!H13,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="35">
+        <f>'UC3'!C13</f>
+        <v>2</v>
+      </c>
+      <c r="G17" s="35" t="str">
+        <f>IF('UC3'!J13="","",'UC3'!J13)</f>
+        <v/>
+      </c>
+      <c r="H17" s="36" t="b">
+        <f>'UC3'!K13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="str">
+        <f>'UC3'!A14&amp;IF('UC3'!K14=TRUE," *","")&amp;IF('UC3'!I14="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0014</v>
+      </c>
+      <c r="B18" s="34">
+        <f>IF('UC3'!H14="","",'UC3'!H14)</f>
+        <v>6</v>
+      </c>
+      <c r="C18" s="35" t="str">
+        <f>'UC3'!I14</f>
+        <v>RISING</v>
+      </c>
+      <c r="D18" s="34">
+        <f>IF('UC3'!I14="RISING",'UC3'!H14,NA())</f>
+        <v>6</v>
+      </c>
+      <c r="E18" s="34" t="e">
+        <f>IF('UC3'!I14="STABLE",'UC3'!H14,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="35">
+        <f>'UC3'!C14</f>
+        <v>2</v>
+      </c>
+      <c r="G18" s="35" t="str">
+        <f>IF('UC3'!J14="","",'UC3'!J14)</f>
+        <v/>
+      </c>
+      <c r="H18" s="36" t="b">
+        <f>'UC3'!K14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="str">
+        <f>'UC3'!A15&amp;IF('UC3'!K15=TRUE," *","")&amp;IF('UC3'!I15="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0015</v>
+      </c>
+      <c r="B19" s="34">
+        <f>IF('UC3'!H15="","",'UC3'!H15)</f>
+        <v>-1</v>
+      </c>
+      <c r="C19" s="35" t="str">
+        <f>'UC3'!I15</f>
+        <v>STABLE</v>
+      </c>
+      <c r="D19" s="34" t="e">
+        <f>IF('UC3'!I15="RISING",'UC3'!H15,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="34">
+        <f>IF('UC3'!I15="STABLE",'UC3'!H15,NA())</f>
+        <v>-1</v>
+      </c>
+      <c r="F19" s="35">
+        <f>'UC3'!C15</f>
+        <v>2</v>
+      </c>
+      <c r="G19" s="35" t="str">
+        <f>IF('UC3'!J15="","",'UC3'!J15)</f>
+        <v/>
+      </c>
+      <c r="H19" s="36" t="b">
+        <f>'UC3'!K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="33" t="str">
+        <f>'UC3'!A16&amp;IF('UC3'!K16=TRUE," *","")&amp;IF('UC3'!I16="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0016 *</v>
+      </c>
+      <c r="B20" s="34">
+        <f>IF('UC3'!H16="","",'UC3'!H16)</f>
+        <v>12</v>
+      </c>
+      <c r="C20" s="35" t="str">
+        <f>'UC3'!I16</f>
+        <v>RISING</v>
+      </c>
+      <c r="D20" s="34">
+        <f>IF('UC3'!I16="RISING",'UC3'!H16,NA())</f>
+        <v>12</v>
+      </c>
+      <c r="E20" s="34" t="e">
+        <f>IF('UC3'!I16="STABLE",'UC3'!H16,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="35">
+        <f>'UC3'!C16</f>
+        <v>2</v>
+      </c>
+      <c r="G20" s="35">
+        <f>IF('UC3'!J16="","",'UC3'!J16)</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="36" t="b">
+        <f>'UC3'!K16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="37" t="str">
+        <f>'UC3'!A17&amp;IF('UC3'!K17=TRUE," *","")&amp;IF('UC3'!I17="INSUFFICIENT_HISTORY"," (1 test)","")</f>
+        <v>GL-0017 (1 test)</v>
+      </c>
+      <c r="B21" s="38" t="str">
+        <f>IF('UC3'!H17="","",'UC3'!H17)</f>
+        <v/>
+      </c>
+      <c r="C21" s="15" t="str">
+        <f>'UC3'!I17</f>
+        <v>INSUFFICIENT_HISTORY</v>
+      </c>
+      <c r="D21" s="38" t="e">
+        <f>IF('UC3'!I17="RISING",'UC3'!H17,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="38" t="e">
+        <f>IF('UC3'!I17="STABLE",'UC3'!H17,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="15">
+        <f>'UC3'!C17</f>
+        <v>1</v>
+      </c>
+      <c r="G21" s="15">
+        <f>IF('UC3'!J17="","",'UC3'!J17)</f>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="H21" s="39" t="b">
+        <f>'UC3'!K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34756B46-37E2-834C-9EF2-57F95F4F90C1}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="36">
+        <f>COUNTIF('UC4'!C:C,A6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="39">
+        <f>COUNTIF('UC4'!C:C,A7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8">
+        <f>SUM(B6:B7)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="33" t="str">
+        <f>IF('UC4'!A2="","",'UC4'!A2)</f>
+        <v>GL-0004</v>
+      </c>
+      <c r="B25" s="35" t="str">
+        <f>IF('UC4'!B2="","",'UC4'!B2)</f>
+        <v>Olivia Brown</v>
+      </c>
+      <c r="C25" s="35" t="str">
+        <f>IF('UC4'!C2="","",'UC4'!C2)</f>
+        <v>RESULT_NOT_RETURNED</v>
+      </c>
+      <c r="D25" s="45">
+        <f>IF('UC4'!E2="","",'UC4'!E2)</f>
+        <v>46087</v>
+      </c>
+      <c r="E25" s="46" t="str">
+        <f>IF('UC4'!D2="","",'UC4'!D2)</f>
+        <v>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</v>
+      </c>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="47"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="37" t="str">
+        <f>IF('UC4'!A3="","",'UC4'!A3)</f>
+        <v>GL-0005</v>
+      </c>
+      <c r="B26" s="15" t="str">
+        <f>IF('UC4'!B3="","",'UC4'!B3)</f>
+        <v>James Wilson</v>
+      </c>
+      <c r="C26" s="15" t="str">
+        <f>IF('UC4'!C3="","",'UC4'!C3)</f>
+        <v>MULTI_PHARMACY_OVERLAP</v>
+      </c>
+      <c r="D26" s="48">
+        <f>IF('UC4'!E3="","",'UC4'!E3)</f>
+        <v>46132</v>
+      </c>
+      <c r="E26" s="49" t="str">
+        <f>IF('UC4'!D3="","",'UC4'!D3)</f>
+        <v>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</v>
+      </c>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E25:J25"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E24:J24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="28" customWidth="1"/>
@@ -1055,28 +8185,236 @@
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>55</v>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46162</v>
+      </c>
+      <c r="E2" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46204</v>
+      </c>
+      <c r="E3" s="3">
+        <v>58</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45992</v>
+      </c>
+      <c r="E4" s="3">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46054</v>
+      </c>
+      <c r="E6" s="3">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E7" s="3">
+        <v>57</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46244</v>
+      </c>
+      <c r="E8" s="3">
+        <v>58</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E9" s="3">
+        <v>65</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +8423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1095,48 +8433,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3">
         <v>7</v>
@@ -1151,7 +8489,7 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I2" s="4">
         <v>46086</v>
@@ -1165,13 +8503,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D3" s="3">
         <v>3</v>
@@ -1186,7 +8524,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I3" s="4">
         <v>46086</v>
@@ -1200,13 +8538,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D4" s="3">
         <v>6</v>
@@ -1221,7 +8559,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I4" s="4">
         <v>46086</v>
@@ -1235,13 +8573,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D5" s="3">
         <v>8</v>
@@ -1256,7 +8594,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I5" s="4">
         <v>46086</v>
@@ -1270,13 +8608,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -1291,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I6" s="4">
         <v>46086</v>
@@ -1305,13 +8643,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
@@ -1326,7 +8664,7 @@
         <v>0.97799999999999998</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I7" s="4">
         <v>46086</v>
@@ -1340,13 +8678,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
@@ -1361,7 +8699,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I8" s="4">
         <v>46086</v>
@@ -1375,13 +8713,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -1396,7 +8734,7 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I9" s="4">
         <v>46086</v>
@@ -1410,13 +8748,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3">
         <v>6</v>
@@ -1431,7 +8769,7 @@
         <v>0.97199999999999998</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I10" s="4">
         <v>46086</v>
@@ -1445,13 +8783,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3">
         <v>7</v>
@@ -1466,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I11" s="4">
         <v>46086</v>
@@ -1480,13 +8818,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D12" s="3">
         <v>6</v>
@@ -1501,7 +8839,7 @@
         <v>0.91700000000000004</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I12" s="4">
         <v>46086</v>
@@ -1517,87 +8855,4 @@
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="12" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="5" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
+++ b/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Project/glucolink-a2/docs/excel_reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BAC49-4570-CC41-83F3-D51EA4CB1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B801291-B1F7-7B49-90FB-8C287B83C654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20160" windowHeight="19280" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="21220" windowHeight="19280" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'UC2'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'UC3'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UC4'!$A$1:$E$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'UC1 Dashboard'!$B$5</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'UC1 Dashboard'!$B$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -574,8 +568,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="171" formatCode="d/mm/yyyy;@"/>
-    <numFmt numFmtId="173" formatCode="\+0.00;\-0.00;0"/>
+    <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="\+0.00;\-0.00;0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -848,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -885,40 +879,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -926,19 +919,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1514,7 +1502,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-AU" altLang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2059,7 +2047,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-AU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2622,7 +2610,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5133,14 +5121,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6680,43 +6668,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -6781,7 +6769,7 @@
       <c r="C26" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="22" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -6807,7 +6795,7 @@
         <f>IF('UC1'!C2="","",'UC1'!C2)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="23">
         <f>IF('UC1'!D2="","",'UC1'!D2)</f>
         <v>46162</v>
       </c>
@@ -6837,7 +6825,7 @@
         <f>IF('UC1'!C3="","",'UC1'!C3)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="23">
         <f>IF('UC1'!D3="","",'UC1'!D3)</f>
         <v>46204</v>
       </c>
@@ -6863,7 +6851,7 @@
         <f>IF('UC1'!C4="","",'UC1'!C4)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="23">
         <f>IF('UC1'!D4="","",'UC1'!D4)</f>
         <v>45992</v>
       </c>
@@ -6889,7 +6877,7 @@
         <f>IF('UC1'!C5="","",'UC1'!C5)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D30" s="25" t="str">
+      <c r="D30" s="23" t="str">
         <f>IF('UC1'!D5="","",'UC1'!D5)</f>
         <v/>
       </c>
@@ -6915,7 +6903,7 @@
         <f>IF('UC1'!C6="","",'UC1'!C6)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="23">
         <f>IF('UC1'!D6="","",'UC1'!D6)</f>
         <v>46054</v>
       </c>
@@ -6941,7 +6929,7 @@
         <f>IF('UC1'!C7="","",'UC1'!C7)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="23">
         <f>IF('UC1'!D7="","",'UC1'!D7)</f>
         <v>46152</v>
       </c>
@@ -6967,7 +6955,7 @@
         <f>IF('UC1'!C8="","",'UC1'!C8)</f>
         <v>Penrith GP Clinic</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="23">
         <f>IF('UC1'!D8="","",'UC1'!D8)</f>
         <v>46244</v>
       </c>
@@ -6993,7 +6981,7 @@
         <f>IF('UC1'!C9="","",'UC1'!C9)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="23">
         <f>IF('UC1'!D9="","",'UC1'!D9)</f>
         <v>46178</v>
       </c>
@@ -7033,43 +7021,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
@@ -7355,591 +7343,591 @@
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="28"/>
+    <col min="5" max="5" width="10.83203125" style="24"/>
     <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="28" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="str">
+      <c r="A6" s="29" t="str">
         <f>'UC3'!A2&amp;IF('UC3'!K2=TRUE," *","")&amp;IF('UC3'!I2="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0001 *</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="24">
         <f>IF('UC3'!H2="","",'UC3'!H2)</f>
         <v>12</v>
       </c>
-      <c r="C6" s="35" t="str">
+      <c r="C6" t="str">
         <f>'UC3'!I2</f>
         <v>RISING</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="24">
         <f>IF('UC3'!I2="RISING",'UC3'!H2,NA())</f>
         <v>12</v>
       </c>
-      <c r="E6" s="34" t="e">
+      <c r="E6" s="24" t="e">
         <f>IF('UC3'!I2="STABLE",'UC3'!H2,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6">
         <f>'UC3'!C2</f>
         <v>3</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6">
         <f>IF('UC3'!J2="","",'UC3'!J2)</f>
         <v>0.98899999999999999</v>
       </c>
-      <c r="H6" s="36" t="b">
+      <c r="H6" s="30" t="b">
         <f>'UC3'!K2</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="33" t="str">
+      <c r="A7" s="29" t="str">
         <f>'UC3'!A3&amp;IF('UC3'!K3=TRUE," *","")&amp;IF('UC3'!I3="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0002</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="24">
         <f>IF('UC3'!H3="","",'UC3'!H3)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="35" t="str">
+      <c r="C7" t="str">
         <f>'UC3'!I3</f>
         <v>STABLE</v>
       </c>
-      <c r="D7" s="34" t="e">
+      <c r="D7" s="24" t="e">
         <f>IF('UC3'!I3="RISING",'UC3'!H3,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="24">
         <f>IF('UC3'!I3="STABLE",'UC3'!H3,NA())</f>
         <v>0</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7">
         <f>'UC3'!C3</f>
         <v>3</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7">
         <f>IF('UC3'!J3="","",'UC3'!J3)</f>
         <v>0.33300000000000002</v>
       </c>
-      <c r="H7" s="36" t="b">
+      <c r="H7" s="30" t="b">
         <f>'UC3'!K3</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="str">
+      <c r="A8" s="29" t="str">
         <f>'UC3'!A4&amp;IF('UC3'!K4=TRUE," *","")&amp;IF('UC3'!I4="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0003 (1 test)</v>
       </c>
-      <c r="B8" s="34" t="str">
+      <c r="B8" s="24" t="str">
         <f>IF('UC3'!H4="","",'UC3'!H4)</f>
         <v/>
       </c>
-      <c r="C8" s="35" t="str">
+      <c r="C8" t="str">
         <f>'UC3'!I4</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D8" s="34" t="e">
+      <c r="D8" s="24" t="e">
         <f>IF('UC3'!I4="RISING",'UC3'!H4,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E8" s="34" t="e">
+      <c r="E8" s="24" t="e">
         <f>IF('UC3'!I4="STABLE",'UC3'!H4,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8">
         <f>'UC3'!C4</f>
         <v>1</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8">
         <f>IF('UC3'!J4="","",'UC3'!J4)</f>
         <v>0.97799999999999998</v>
       </c>
-      <c r="H8" s="36" t="b">
+      <c r="H8" s="30" t="b">
         <f>'UC3'!K4</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="33" t="str">
+      <c r="A9" s="29" t="str">
         <f>'UC3'!A5&amp;IF('UC3'!K5=TRUE," *","")&amp;IF('UC3'!I5="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0004</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="24">
         <f>IF('UC3'!H5="","",'UC3'!H5)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="35" t="str">
+      <c r="C9" t="str">
         <f>'UC3'!I5</f>
         <v>STABLE</v>
       </c>
-      <c r="D9" s="34" t="e">
+      <c r="D9" s="24" t="e">
         <f>IF('UC3'!I5="RISING",'UC3'!H5,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="24">
         <f>IF('UC3'!I5="STABLE",'UC3'!H5,NA())</f>
         <v>1</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9">
         <f>'UC3'!C5</f>
         <v>2</v>
       </c>
-      <c r="G9" s="35" t="str">
+      <c r="G9" t="str">
         <f>IF('UC3'!J5="","",'UC3'!J5)</f>
         <v/>
       </c>
-      <c r="H9" s="36" t="b">
+      <c r="H9" s="30" t="b">
         <f>'UC3'!K5</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="33" t="str">
+      <c r="A10" s="29" t="str">
         <f>'UC3'!A6&amp;IF('UC3'!K6=TRUE," *","")&amp;IF('UC3'!I6="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0005</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="24">
         <f>IF('UC3'!H6="","",'UC3'!H6)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="C10" s="35" t="str">
+      <c r="C10" t="str">
         <f>'UC3'!I6</f>
         <v>STABLE</v>
       </c>
-      <c r="D10" s="34" t="e">
+      <c r="D10" s="24" t="e">
         <f>IF('UC3'!I6="RISING",'UC3'!H6,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="24">
         <f>IF('UC3'!I6="STABLE",'UC3'!H6,NA())</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10">
         <f>'UC3'!C6</f>
         <v>2</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10">
         <f>IF('UC3'!J6="","",'UC3'!J6)</f>
         <v>0.97199999999999998</v>
       </c>
-      <c r="H10" s="36" t="b">
+      <c r="H10" s="30" t="b">
         <f>'UC3'!K6</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="str">
+      <c r="A11" s="29" t="str">
         <f>'UC3'!A7&amp;IF('UC3'!K7=TRUE," *","")&amp;IF('UC3'!I7="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0007 (1 test)</v>
       </c>
-      <c r="B11" s="34" t="str">
+      <c r="B11" s="24" t="str">
         <f>IF('UC3'!H7="","",'UC3'!H7)</f>
         <v/>
       </c>
-      <c r="C11" s="35" t="str">
+      <c r="C11" t="str">
         <f>'UC3'!I7</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D11" s="34" t="e">
+      <c r="D11" s="24" t="e">
         <f>IF('UC3'!I7="RISING",'UC3'!H7,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E11" s="34" t="e">
+      <c r="E11" s="24" t="e">
         <f>IF('UC3'!I7="STABLE",'UC3'!H7,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11">
         <f>'UC3'!C7</f>
         <v>1</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11">
         <f>IF('UC3'!J7="","",'UC3'!J7)</f>
         <v>1</v>
       </c>
-      <c r="H11" s="36" t="b">
+      <c r="H11" s="30" t="b">
         <f>'UC3'!K7</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="str">
+      <c r="A12" s="29" t="str">
         <f>'UC3'!A8&amp;IF('UC3'!K8=TRUE," *","")&amp;IF('UC3'!I8="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0008</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="24">
         <f>IF('UC3'!H8="","",'UC3'!H8)</f>
         <v>-1</v>
       </c>
-      <c r="C12" s="35" t="str">
+      <c r="C12" t="str">
         <f>'UC3'!I8</f>
         <v>STABLE</v>
       </c>
-      <c r="D12" s="34" t="e">
+      <c r="D12" s="24" t="e">
         <f>IF('UC3'!I8="RISING",'UC3'!H8,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="24">
         <f>IF('UC3'!I8="STABLE",'UC3'!H8,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12">
         <f>'UC3'!C8</f>
         <v>2</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12">
         <f>IF('UC3'!J8="","",'UC3'!J8)</f>
         <v>0.97799999999999998</v>
       </c>
-      <c r="H12" s="36" t="b">
+      <c r="H12" s="30" t="b">
         <f>'UC3'!K8</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="str">
+      <c r="A13" s="29" t="str">
         <f>'UC3'!A9&amp;IF('UC3'!K9=TRUE," *","")&amp;IF('UC3'!I9="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0009</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="24">
         <f>IF('UC3'!H9="","",'UC3'!H9)</f>
         <v>-1</v>
       </c>
-      <c r="C13" s="35" t="str">
+      <c r="C13" t="str">
         <f>'UC3'!I9</f>
         <v>STABLE</v>
       </c>
-      <c r="D13" s="34" t="e">
+      <c r="D13" s="24" t="e">
         <f>IF('UC3'!I9="RISING",'UC3'!H9,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="24">
         <f>IF('UC3'!I9="STABLE",'UC3'!H9,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13">
         <f>'UC3'!C9</f>
         <v>4</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13">
         <f>IF('UC3'!J9="","",'UC3'!J9)</f>
         <v>1</v>
       </c>
-      <c r="H13" s="36" t="b">
+      <c r="H13" s="30" t="b">
         <f>'UC3'!K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="29" t="str">
         <f>'UC3'!A10&amp;IF('UC3'!K10=TRUE," *","")&amp;IF('UC3'!I10="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0010 (1 test)</v>
       </c>
-      <c r="B14" s="34" t="str">
+      <c r="B14" s="24" t="str">
         <f>IF('UC3'!H10="","",'UC3'!H10)</f>
         <v/>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" t="str">
         <f>'UC3'!I10</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D14" s="34" t="e">
+      <c r="D14" s="24" t="e">
         <f>IF('UC3'!I10="RISING",'UC3'!H10,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E14" s="34" t="e">
+      <c r="E14" s="24" t="e">
         <f>IF('UC3'!I10="STABLE",'UC3'!H10,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14">
         <f>'UC3'!C10</f>
         <v>1</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14">
         <f>IF('UC3'!J10="","",'UC3'!J10)</f>
         <v>0.5</v>
       </c>
-      <c r="H14" s="36" t="b">
+      <c r="H14" s="30" t="b">
         <f>'UC3'!K10</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="str">
+      <c r="A15" s="29" t="str">
         <f>'UC3'!A11&amp;IF('UC3'!K11=TRUE," *","")&amp;IF('UC3'!I11="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0011</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="24">
         <f>IF('UC3'!H11="","",'UC3'!H11)</f>
         <v>-4</v>
       </c>
-      <c r="C15" s="35" t="str">
+      <c r="C15" t="str">
         <f>'UC3'!I11</f>
         <v>STABLE</v>
       </c>
-      <c r="D15" s="34" t="e">
+      <c r="D15" s="24" t="e">
         <f>IF('UC3'!I11="RISING",'UC3'!H11,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="24">
         <f>IF('UC3'!I11="STABLE",'UC3'!H11,NA())</f>
         <v>-4</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15">
         <f>'UC3'!C11</f>
         <v>2</v>
       </c>
-      <c r="G15" s="35" t="str">
+      <c r="G15" t="str">
         <f>IF('UC3'!J11="","",'UC3'!J11)</f>
         <v/>
       </c>
-      <c r="H15" s="36" t="b">
+      <c r="H15" s="30" t="b">
         <f>'UC3'!K11</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="str">
+      <c r="A16" s="29" t="str">
         <f>'UC3'!A12&amp;IF('UC3'!K12=TRUE," *","")&amp;IF('UC3'!I12="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0012 (1 test)</v>
       </c>
-      <c r="B16" s="34" t="str">
+      <c r="B16" s="24" t="str">
         <f>IF('UC3'!H12="","",'UC3'!H12)</f>
         <v/>
       </c>
-      <c r="C16" s="35" t="str">
+      <c r="C16" t="str">
         <f>'UC3'!I12</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D16" s="34" t="e">
+      <c r="D16" s="24" t="e">
         <f>IF('UC3'!I12="RISING",'UC3'!H12,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E16" s="34" t="e">
+      <c r="E16" s="24" t="e">
         <f>IF('UC3'!I12="STABLE",'UC3'!H12,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16">
         <f>'UC3'!C12</f>
         <v>1</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16">
         <f>IF('UC3'!J12="","",'UC3'!J12)</f>
         <v>0.97199999999999998</v>
       </c>
-      <c r="H16" s="36" t="b">
+      <c r="H16" s="30" t="b">
         <f>'UC3'!K12</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="str">
+      <c r="A17" s="29" t="str">
         <f>'UC3'!A13&amp;IF('UC3'!K13=TRUE," *","")&amp;IF('UC3'!I13="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0013</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="24">
         <f>IF('UC3'!H13="","",'UC3'!H13)</f>
         <v>5</v>
       </c>
-      <c r="C17" s="35" t="str">
+      <c r="C17" t="str">
         <f>'UC3'!I13</f>
         <v>RISING</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="24">
         <f>IF('UC3'!I13="RISING",'UC3'!H13,NA())</f>
         <v>5</v>
       </c>
-      <c r="E17" s="34" t="e">
+      <c r="E17" s="24" t="e">
         <f>IF('UC3'!I13="STABLE",'UC3'!H13,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17">
         <f>'UC3'!C13</f>
         <v>2</v>
       </c>
-      <c r="G17" s="35" t="str">
+      <c r="G17" t="str">
         <f>IF('UC3'!J13="","",'UC3'!J13)</f>
         <v/>
       </c>
-      <c r="H17" s="36" t="b">
+      <c r="H17" s="30" t="b">
         <f>'UC3'!K13</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="str">
+      <c r="A18" s="29" t="str">
         <f>'UC3'!A14&amp;IF('UC3'!K14=TRUE," *","")&amp;IF('UC3'!I14="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0014</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="24">
         <f>IF('UC3'!H14="","",'UC3'!H14)</f>
         <v>6</v>
       </c>
-      <c r="C18" s="35" t="str">
+      <c r="C18" t="str">
         <f>'UC3'!I14</f>
         <v>RISING</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="24">
         <f>IF('UC3'!I14="RISING",'UC3'!H14,NA())</f>
         <v>6</v>
       </c>
-      <c r="E18" s="34" t="e">
+      <c r="E18" s="24" t="e">
         <f>IF('UC3'!I14="STABLE",'UC3'!H14,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18">
         <f>'UC3'!C14</f>
         <v>2</v>
       </c>
-      <c r="G18" s="35" t="str">
+      <c r="G18" t="str">
         <f>IF('UC3'!J14="","",'UC3'!J14)</f>
         <v/>
       </c>
-      <c r="H18" s="36" t="b">
+      <c r="H18" s="30" t="b">
         <f>'UC3'!K14</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="str">
+      <c r="A19" s="29" t="str">
         <f>'UC3'!A15&amp;IF('UC3'!K15=TRUE," *","")&amp;IF('UC3'!I15="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0015</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="24">
         <f>IF('UC3'!H15="","",'UC3'!H15)</f>
         <v>-1</v>
       </c>
-      <c r="C19" s="35" t="str">
+      <c r="C19" t="str">
         <f>'UC3'!I15</f>
         <v>STABLE</v>
       </c>
-      <c r="D19" s="34" t="e">
+      <c r="D19" s="24" t="e">
         <f>IF('UC3'!I15="RISING",'UC3'!H15,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="24">
         <f>IF('UC3'!I15="STABLE",'UC3'!H15,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19">
         <f>'UC3'!C15</f>
         <v>2</v>
       </c>
-      <c r="G19" s="35" t="str">
+      <c r="G19" t="str">
         <f>IF('UC3'!J15="","",'UC3'!J15)</f>
         <v/>
       </c>
-      <c r="H19" s="36" t="b">
+      <c r="H19" s="30" t="b">
         <f>'UC3'!K15</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="29" t="str">
         <f>'UC3'!A16&amp;IF('UC3'!K16=TRUE," *","")&amp;IF('UC3'!I16="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0016 *</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="24">
         <f>IF('UC3'!H16="","",'UC3'!H16)</f>
         <v>12</v>
       </c>
-      <c r="C20" s="35" t="str">
+      <c r="C20" t="str">
         <f>'UC3'!I16</f>
         <v>RISING</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="24">
         <f>IF('UC3'!I16="RISING",'UC3'!H16,NA())</f>
         <v>12</v>
       </c>
-      <c r="E20" s="34" t="e">
+      <c r="E20" s="24" t="e">
         <f>IF('UC3'!I16="STABLE",'UC3'!H16,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20">
         <f>'UC3'!C16</f>
         <v>2</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20">
         <f>IF('UC3'!J16="","",'UC3'!J16)</f>
         <v>1</v>
       </c>
-      <c r="H20" s="36" t="b">
+      <c r="H20" s="30" t="b">
         <f>'UC3'!K16</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="37" t="str">
+      <c r="A21" s="31" t="str">
         <f>'UC3'!A17&amp;IF('UC3'!K17=TRUE," *","")&amp;IF('UC3'!I17="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0017 (1 test)</v>
       </c>
-      <c r="B21" s="38" t="str">
+      <c r="B21" s="32" t="str">
         <f>IF('UC3'!H17="","",'UC3'!H17)</f>
         <v/>
       </c>
@@ -7947,11 +7935,11 @@
         <f>'UC3'!I17</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D21" s="38" t="e">
+      <c r="D21" s="32" t="e">
         <f>IF('UC3'!I17="RISING",'UC3'!H17,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E21" s="38" t="e">
+      <c r="E21" s="32" t="e">
         <f>IF('UC3'!I17="STABLE",'UC3'!H17,NA())</f>
         <v>#N/A</v>
       </c>
@@ -7963,22 +7951,22 @@
         <f>IF('UC3'!J17="","",'UC3'!J17)</f>
         <v>0.91700000000000004</v>
       </c>
-      <c r="H21" s="39" t="b">
+      <c r="H21" s="33" t="b">
         <f>'UC3'!K17</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8003,75 +7991,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="28" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="30">
         <f>COUNTIF('UC4'!C:C,A6)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="33">
         <f>COUNTIF('UC4'!C:C,A7)</f>
         <v>1</v>
       </c>
@@ -8086,56 +8074,56 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="44"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="33" t="str">
+      <c r="A25" s="29" t="str">
         <f>IF('UC4'!A2="","",'UC4'!A2)</f>
         <v>GL-0004</v>
       </c>
-      <c r="B25" s="35" t="str">
+      <c r="B25" t="str">
         <f>IF('UC4'!B2="","",'UC4'!B2)</f>
         <v>Olivia Brown</v>
       </c>
-      <c r="C25" s="35" t="str">
+      <c r="C25" t="str">
         <f>IF('UC4'!C2="","",'UC4'!C2)</f>
         <v>RESULT_NOT_RETURNED</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="8">
         <f>IF('UC4'!E2="","",'UC4'!E2)</f>
         <v>46087</v>
       </c>
-      <c r="E25" s="46" t="str">
+      <c r="E25" s="35" t="str">
         <f>IF('UC4'!D2="","",'UC4'!D2)</f>
         <v>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="47"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="36"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="37" t="str">
+      <c r="A26" s="31" t="str">
         <f>IF('UC4'!A3="","",'UC4'!A3)</f>
         <v>GL-0005</v>
       </c>
@@ -8147,19 +8135,19 @@
         <f>IF('UC4'!C3="","",'UC4'!C3)</f>
         <v>MULTI_PHARMACY_OVERLAP</v>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="34">
         <f>IF('UC4'!E3="","",'UC4'!E3)</f>
         <v>46132</v>
       </c>
-      <c r="E26" s="49" t="str">
+      <c r="E26" s="37" t="str">
         <f>IF('UC4'!D3="","",'UC4'!D3)</f>
         <v>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</v>
       </c>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="50"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
+++ b/docs/excel_reporting/F_Reporting_Dashboard_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhakim/Project/glucolink-a2/docs/excel_reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44BAC49-4570-CC41-83F3-D51EA4CB1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67D4A2A-AD1B-954C-9924-A391F14B91A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20160" windowHeight="19280" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19360" yWindow="740" windowWidth="20160" windowHeight="19280" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -30,14 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'UC2'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'UC3'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UC4'!$A$1:$E$1</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'UC1 Dashboard'!$B$5</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'UC1 Dashboard'!$A$6:$A$9</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'UC1 Dashboard'!$B$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'UC1 Dashboard'!$B$6:$B$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -77,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="165">
   <si>
     <t>Status</t>
   </si>
@@ -566,6 +560,12 @@
   </si>
   <si>
     <t>breaks</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_uc3_hba1c_trend | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
+  </si>
+  <si>
+    <t>Source: reporting.vw_care_path_breaks | database: glucolink_a2 | commit: 9a499ce | exported 2026-10-14 17:12 | checks: ALL PASS</t>
   </si>
 </sst>
 </file>
@@ -574,8 +574,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="171" formatCode="d/mm/yyyy;@"/>
-    <numFmt numFmtId="173" formatCode="\+0.00;\-0.00;0"/>
+    <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="\+0.00;\-0.00;0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -848,7 +848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -885,40 +885,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -926,19 +925,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1467,7 +1461,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR" baseline="0"/>
-              <a:t>per. atient,</a:t>
+              <a:t>per patient,</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="ko-KR" altLang="en-US" baseline="0"/>
@@ -1514,7 +1508,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-AU" altLang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2059,7 +2053,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-AU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2622,7 +2616,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6385,7 +6379,7 @@
         <v>123</v>
       </c>
       <c r="E2" s="6">
-        <v>46087</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -6680,43 +6674,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -6781,7 +6775,7 @@
       <c r="C26" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="22" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -6807,7 +6801,7 @@
         <f>IF('UC1'!C2="","",'UC1'!C2)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="23">
         <f>IF('UC1'!D2="","",'UC1'!D2)</f>
         <v>46162</v>
       </c>
@@ -6837,7 +6831,7 @@
         <f>IF('UC1'!C3="","",'UC1'!C3)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="23">
         <f>IF('UC1'!D3="","",'UC1'!D3)</f>
         <v>46204</v>
       </c>
@@ -6863,7 +6857,7 @@
         <f>IF('UC1'!C4="","",'UC1'!C4)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="23">
         <f>IF('UC1'!D4="","",'UC1'!D4)</f>
         <v>45992</v>
       </c>
@@ -6889,7 +6883,7 @@
         <f>IF('UC1'!C5="","",'UC1'!C5)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D30" s="25" t="str">
+      <c r="D30" s="23" t="str">
         <f>IF('UC1'!D5="","",'UC1'!D5)</f>
         <v/>
       </c>
@@ -6915,7 +6909,7 @@
         <f>IF('UC1'!C6="","",'UC1'!C6)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="23">
         <f>IF('UC1'!D6="","",'UC1'!D6)</f>
         <v>46054</v>
       </c>
@@ -6941,7 +6935,7 @@
         <f>IF('UC1'!C7="","",'UC1'!C7)</f>
         <v>Parramatta Family Practice</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="23">
         <f>IF('UC1'!D7="","",'UC1'!D7)</f>
         <v>46152</v>
       </c>
@@ -6967,7 +6961,7 @@
         <f>IF('UC1'!C8="","",'UC1'!C8)</f>
         <v>Penrith GP Clinic</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="23">
         <f>IF('UC1'!D8="","",'UC1'!D8)</f>
         <v>46244</v>
       </c>
@@ -6993,7 +6987,7 @@
         <f>IF('UC1'!C9="","",'UC1'!C9)</f>
         <v>Blacktown Medical Centre</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="23">
         <f>IF('UC1'!D9="","",'UC1'!D9)</f>
         <v>46178</v>
       </c>
@@ -7033,43 +7027,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
@@ -7355,591 +7349,591 @@
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="28"/>
+    <col min="5" max="5" width="10.83203125" style="24"/>
     <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="A2" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="28" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="str">
+      <c r="A6" s="29" t="str">
         <f>'UC3'!A2&amp;IF('UC3'!K2=TRUE," *","")&amp;IF('UC3'!I2="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0001 *</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="24">
         <f>IF('UC3'!H2="","",'UC3'!H2)</f>
         <v>12</v>
       </c>
-      <c r="C6" s="35" t="str">
+      <c r="C6" t="str">
         <f>'UC3'!I2</f>
         <v>RISING</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="24">
         <f>IF('UC3'!I2="RISING",'UC3'!H2,NA())</f>
         <v>12</v>
       </c>
-      <c r="E6" s="34" t="e">
+      <c r="E6" s="24" t="e">
         <f>IF('UC3'!I2="STABLE",'UC3'!H2,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6">
         <f>'UC3'!C2</f>
         <v>3</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6">
         <f>IF('UC3'!J2="","",'UC3'!J2)</f>
         <v>0.98899999999999999</v>
       </c>
-      <c r="H6" s="36" t="b">
+      <c r="H6" s="30" t="b">
         <f>'UC3'!K2</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="33" t="str">
+      <c r="A7" s="29" t="str">
         <f>'UC3'!A3&amp;IF('UC3'!K3=TRUE," *","")&amp;IF('UC3'!I3="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0002</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="24">
         <f>IF('UC3'!H3="","",'UC3'!H3)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="35" t="str">
+      <c r="C7" t="str">
         <f>'UC3'!I3</f>
         <v>STABLE</v>
       </c>
-      <c r="D7" s="34" t="e">
+      <c r="D7" s="24" t="e">
         <f>IF('UC3'!I3="RISING",'UC3'!H3,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="24">
         <f>IF('UC3'!I3="STABLE",'UC3'!H3,NA())</f>
         <v>0</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7">
         <f>'UC3'!C3</f>
         <v>3</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7">
         <f>IF('UC3'!J3="","",'UC3'!J3)</f>
         <v>0.33300000000000002</v>
       </c>
-      <c r="H7" s="36" t="b">
+      <c r="H7" s="30" t="b">
         <f>'UC3'!K3</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="str">
+      <c r="A8" s="29" t="str">
         <f>'UC3'!A4&amp;IF('UC3'!K4=TRUE," *","")&amp;IF('UC3'!I4="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0003 (1 test)</v>
       </c>
-      <c r="B8" s="34" t="str">
+      <c r="B8" s="24" t="str">
         <f>IF('UC3'!H4="","",'UC3'!H4)</f>
         <v/>
       </c>
-      <c r="C8" s="35" t="str">
+      <c r="C8" t="str">
         <f>'UC3'!I4</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D8" s="34" t="e">
+      <c r="D8" s="24" t="e">
         <f>IF('UC3'!I4="RISING",'UC3'!H4,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E8" s="34" t="e">
+      <c r="E8" s="24" t="e">
         <f>IF('UC3'!I4="STABLE",'UC3'!H4,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8">
         <f>'UC3'!C4</f>
         <v>1</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8">
         <f>IF('UC3'!J4="","",'UC3'!J4)</f>
         <v>0.97799999999999998</v>
       </c>
-      <c r="H8" s="36" t="b">
+      <c r="H8" s="30" t="b">
         <f>'UC3'!K4</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="33" t="str">
+      <c r="A9" s="29" t="str">
         <f>'UC3'!A5&amp;IF('UC3'!K5=TRUE," *","")&amp;IF('UC3'!I5="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0004</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="24">
         <f>IF('UC3'!H5="","",'UC3'!H5)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="35" t="str">
+      <c r="C9" t="str">
         <f>'UC3'!I5</f>
         <v>STABLE</v>
       </c>
-      <c r="D9" s="34" t="e">
+      <c r="D9" s="24" t="e">
         <f>IF('UC3'!I5="RISING",'UC3'!H5,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="24">
         <f>IF('UC3'!I5="STABLE",'UC3'!H5,NA())</f>
         <v>1</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9">
         <f>'UC3'!C5</f>
         <v>2</v>
       </c>
-      <c r="G9" s="35" t="str">
+      <c r="G9" t="str">
         <f>IF('UC3'!J5="","",'UC3'!J5)</f>
         <v/>
       </c>
-      <c r="H9" s="36" t="b">
+      <c r="H9" s="30" t="b">
         <f>'UC3'!K5</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="33" t="str">
+      <c r="A10" s="29" t="str">
         <f>'UC3'!A6&amp;IF('UC3'!K6=TRUE," *","")&amp;IF('UC3'!I6="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0005</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="24">
         <f>IF('UC3'!H6="","",'UC3'!H6)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="C10" s="35" t="str">
+      <c r="C10" t="str">
         <f>'UC3'!I6</f>
         <v>STABLE</v>
       </c>
-      <c r="D10" s="34" t="e">
+      <c r="D10" s="24" t="e">
         <f>IF('UC3'!I6="RISING",'UC3'!H6,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="24">
         <f>IF('UC3'!I6="STABLE",'UC3'!H6,NA())</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10">
         <f>'UC3'!C6</f>
         <v>2</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10">
         <f>IF('UC3'!J6="","",'UC3'!J6)</f>
         <v>0.97199999999999998</v>
       </c>
-      <c r="H10" s="36" t="b">
+      <c r="H10" s="30" t="b">
         <f>'UC3'!K6</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="str">
+      <c r="A11" s="29" t="str">
         <f>'UC3'!A7&amp;IF('UC3'!K7=TRUE," *","")&amp;IF('UC3'!I7="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0007 (1 test)</v>
       </c>
-      <c r="B11" s="34" t="str">
+      <c r="B11" s="24" t="str">
         <f>IF('UC3'!H7="","",'UC3'!H7)</f>
         <v/>
       </c>
-      <c r="C11" s="35" t="str">
+      <c r="C11" t="str">
         <f>'UC3'!I7</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D11" s="34" t="e">
+      <c r="D11" s="24" t="e">
         <f>IF('UC3'!I7="RISING",'UC3'!H7,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E11" s="34" t="e">
+      <c r="E11" s="24" t="e">
         <f>IF('UC3'!I7="STABLE",'UC3'!H7,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11">
         <f>'UC3'!C7</f>
         <v>1</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11">
         <f>IF('UC3'!J7="","",'UC3'!J7)</f>
         <v>1</v>
       </c>
-      <c r="H11" s="36" t="b">
+      <c r="H11" s="30" t="b">
         <f>'UC3'!K7</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="str">
+      <c r="A12" s="29" t="str">
         <f>'UC3'!A8&amp;IF('UC3'!K8=TRUE," *","")&amp;IF('UC3'!I8="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0008</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="24">
         <f>IF('UC3'!H8="","",'UC3'!H8)</f>
         <v>-1</v>
       </c>
-      <c r="C12" s="35" t="str">
+      <c r="C12" t="str">
         <f>'UC3'!I8</f>
         <v>STABLE</v>
       </c>
-      <c r="D12" s="34" t="e">
+      <c r="D12" s="24" t="e">
         <f>IF('UC3'!I8="RISING",'UC3'!H8,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="24">
         <f>IF('UC3'!I8="STABLE",'UC3'!H8,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12">
         <f>'UC3'!C8</f>
         <v>2</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12">
         <f>IF('UC3'!J8="","",'UC3'!J8)</f>
         <v>0.97799999999999998</v>
       </c>
-      <c r="H12" s="36" t="b">
+      <c r="H12" s="30" t="b">
         <f>'UC3'!K8</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="str">
+      <c r="A13" s="29" t="str">
         <f>'UC3'!A9&amp;IF('UC3'!K9=TRUE," *","")&amp;IF('UC3'!I9="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0009</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="24">
         <f>IF('UC3'!H9="","",'UC3'!H9)</f>
         <v>-1</v>
       </c>
-      <c r="C13" s="35" t="str">
+      <c r="C13" t="str">
         <f>'UC3'!I9</f>
         <v>STABLE</v>
       </c>
-      <c r="D13" s="34" t="e">
+      <c r="D13" s="24" t="e">
         <f>IF('UC3'!I9="RISING",'UC3'!H9,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="24">
         <f>IF('UC3'!I9="STABLE",'UC3'!H9,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13">
         <f>'UC3'!C9</f>
         <v>4</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13">
         <f>IF('UC3'!J9="","",'UC3'!J9)</f>
         <v>1</v>
       </c>
-      <c r="H13" s="36" t="b">
+      <c r="H13" s="30" t="b">
         <f>'UC3'!K9</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="29" t="str">
         <f>'UC3'!A10&amp;IF('UC3'!K10=TRUE," *","")&amp;IF('UC3'!I10="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0010 (1 test)</v>
       </c>
-      <c r="B14" s="34" t="str">
+      <c r="B14" s="24" t="str">
         <f>IF('UC3'!H10="","",'UC3'!H10)</f>
         <v/>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" t="str">
         <f>'UC3'!I10</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D14" s="34" t="e">
+      <c r="D14" s="24" t="e">
         <f>IF('UC3'!I10="RISING",'UC3'!H10,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E14" s="34" t="e">
+      <c r="E14" s="24" t="e">
         <f>IF('UC3'!I10="STABLE",'UC3'!H10,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14">
         <f>'UC3'!C10</f>
         <v>1</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14">
         <f>IF('UC3'!J10="","",'UC3'!J10)</f>
         <v>0.5</v>
       </c>
-      <c r="H14" s="36" t="b">
+      <c r="H14" s="30" t="b">
         <f>'UC3'!K10</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="str">
+      <c r="A15" s="29" t="str">
         <f>'UC3'!A11&amp;IF('UC3'!K11=TRUE," *","")&amp;IF('UC3'!I11="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0011</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="24">
         <f>IF('UC3'!H11="","",'UC3'!H11)</f>
         <v>-4</v>
       </c>
-      <c r="C15" s="35" t="str">
+      <c r="C15" t="str">
         <f>'UC3'!I11</f>
         <v>STABLE</v>
       </c>
-      <c r="D15" s="34" t="e">
+      <c r="D15" s="24" t="e">
         <f>IF('UC3'!I11="RISING",'UC3'!H11,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="24">
         <f>IF('UC3'!I11="STABLE",'UC3'!H11,NA())</f>
         <v>-4</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15">
         <f>'UC3'!C11</f>
         <v>2</v>
       </c>
-      <c r="G15" s="35" t="str">
+      <c r="G15" t="str">
         <f>IF('UC3'!J11="","",'UC3'!J11)</f>
         <v/>
       </c>
-      <c r="H15" s="36" t="b">
+      <c r="H15" s="30" t="b">
         <f>'UC3'!K11</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="str">
+      <c r="A16" s="29" t="str">
         <f>'UC3'!A12&amp;IF('UC3'!K12=TRUE," *","")&amp;IF('UC3'!I12="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0012 (1 test)</v>
       </c>
-      <c r="B16" s="34" t="str">
+      <c r="B16" s="24" t="str">
         <f>IF('UC3'!H12="","",'UC3'!H12)</f>
         <v/>
       </c>
-      <c r="C16" s="35" t="str">
+      <c r="C16" t="str">
         <f>'UC3'!I12</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D16" s="34" t="e">
+      <c r="D16" s="24" t="e">
         <f>IF('UC3'!I12="RISING",'UC3'!H12,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E16" s="34" t="e">
+      <c r="E16" s="24" t="e">
         <f>IF('UC3'!I12="STABLE",'UC3'!H12,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16">
         <f>'UC3'!C12</f>
         <v>1</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16">
         <f>IF('UC3'!J12="","",'UC3'!J12)</f>
         <v>0.97199999999999998</v>
       </c>
-      <c r="H16" s="36" t="b">
+      <c r="H16" s="30" t="b">
         <f>'UC3'!K12</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="str">
+      <c r="A17" s="29" t="str">
         <f>'UC3'!A13&amp;IF('UC3'!K13=TRUE," *","")&amp;IF('UC3'!I13="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0013</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="24">
         <f>IF('UC3'!H13="","",'UC3'!H13)</f>
         <v>5</v>
       </c>
-      <c r="C17" s="35" t="str">
+      <c r="C17" t="str">
         <f>'UC3'!I13</f>
         <v>RISING</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="24">
         <f>IF('UC3'!I13="RISING",'UC3'!H13,NA())</f>
         <v>5</v>
       </c>
-      <c r="E17" s="34" t="e">
+      <c r="E17" s="24" t="e">
         <f>IF('UC3'!I13="STABLE",'UC3'!H13,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17">
         <f>'UC3'!C13</f>
         <v>2</v>
       </c>
-      <c r="G17" s="35" t="str">
+      <c r="G17" t="str">
         <f>IF('UC3'!J13="","",'UC3'!J13)</f>
         <v/>
       </c>
-      <c r="H17" s="36" t="b">
+      <c r="H17" s="30" t="b">
         <f>'UC3'!K13</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="str">
+      <c r="A18" s="29" t="str">
         <f>'UC3'!A14&amp;IF('UC3'!K14=TRUE," *","")&amp;IF('UC3'!I14="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0014</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="24">
         <f>IF('UC3'!H14="","",'UC3'!H14)</f>
         <v>6</v>
       </c>
-      <c r="C18" s="35" t="str">
+      <c r="C18" t="str">
         <f>'UC3'!I14</f>
         <v>RISING</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="24">
         <f>IF('UC3'!I14="RISING",'UC3'!H14,NA())</f>
         <v>6</v>
       </c>
-      <c r="E18" s="34" t="e">
+      <c r="E18" s="24" t="e">
         <f>IF('UC3'!I14="STABLE",'UC3'!H14,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18">
         <f>'UC3'!C14</f>
         <v>2</v>
       </c>
-      <c r="G18" s="35" t="str">
+      <c r="G18" t="str">
         <f>IF('UC3'!J14="","",'UC3'!J14)</f>
         <v/>
       </c>
-      <c r="H18" s="36" t="b">
+      <c r="H18" s="30" t="b">
         <f>'UC3'!K14</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="str">
+      <c r="A19" s="29" t="str">
         <f>'UC3'!A15&amp;IF('UC3'!K15=TRUE," *","")&amp;IF('UC3'!I15="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0015</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="24">
         <f>IF('UC3'!H15="","",'UC3'!H15)</f>
         <v>-1</v>
       </c>
-      <c r="C19" s="35" t="str">
+      <c r="C19" t="str">
         <f>'UC3'!I15</f>
         <v>STABLE</v>
       </c>
-      <c r="D19" s="34" t="e">
+      <c r="D19" s="24" t="e">
         <f>IF('UC3'!I15="RISING",'UC3'!H15,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="24">
         <f>IF('UC3'!I15="STABLE",'UC3'!H15,NA())</f>
         <v>-1</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19">
         <f>'UC3'!C15</f>
         <v>2</v>
       </c>
-      <c r="G19" s="35" t="str">
+      <c r="G19" t="str">
         <f>IF('UC3'!J15="","",'UC3'!J15)</f>
         <v/>
       </c>
-      <c r="H19" s="36" t="b">
+      <c r="H19" s="30" t="b">
         <f>'UC3'!K15</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="33" t="str">
+      <c r="A20" s="29" t="str">
         <f>'UC3'!A16&amp;IF('UC3'!K16=TRUE," *","")&amp;IF('UC3'!I16="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0016 *</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="24">
         <f>IF('UC3'!H16="","",'UC3'!H16)</f>
         <v>12</v>
       </c>
-      <c r="C20" s="35" t="str">
+      <c r="C20" t="str">
         <f>'UC3'!I16</f>
         <v>RISING</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="24">
         <f>IF('UC3'!I16="RISING",'UC3'!H16,NA())</f>
         <v>12</v>
       </c>
-      <c r="E20" s="34" t="e">
+      <c r="E20" s="24" t="e">
         <f>IF('UC3'!I16="STABLE",'UC3'!H16,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20">
         <f>'UC3'!C16</f>
         <v>2</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20">
         <f>IF('UC3'!J16="","",'UC3'!J16)</f>
         <v>1</v>
       </c>
-      <c r="H20" s="36" t="b">
+      <c r="H20" s="30" t="b">
         <f>'UC3'!K16</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="37" t="str">
+      <c r="A21" s="31" t="str">
         <f>'UC3'!A17&amp;IF('UC3'!K17=TRUE," *","")&amp;IF('UC3'!I17="INSUFFICIENT_HISTORY"," (1 test)","")</f>
         <v>GL-0017 (1 test)</v>
       </c>
-      <c r="B21" s="38" t="str">
+      <c r="B21" s="32" t="str">
         <f>IF('UC3'!H17="","",'UC3'!H17)</f>
         <v/>
       </c>
@@ -7947,11 +7941,11 @@
         <f>'UC3'!I17</f>
         <v>INSUFFICIENT_HISTORY</v>
       </c>
-      <c r="D21" s="38" t="e">
+      <c r="D21" s="32" t="e">
         <f>IF('UC3'!I17="RISING",'UC3'!H17,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E21" s="38" t="e">
+      <c r="E21" s="32" t="e">
         <f>IF('UC3'!I17="STABLE",'UC3'!H17,NA())</f>
         <v>#N/A</v>
       </c>
@@ -7963,22 +7957,22 @@
         <f>IF('UC3'!J17="","",'UC3'!J17)</f>
         <v>0.91700000000000004</v>
       </c>
-      <c r="H21" s="39" t="b">
+      <c r="H21" s="33" t="b">
         <f>'UC3'!K17</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8003,75 +7997,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
+      <c r="A2" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="28" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="30">
         <f>COUNTIF('UC4'!C:C,A6)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="33">
         <f>COUNTIF('UC4'!C:C,A7)</f>
         <v>1</v>
       </c>
@@ -8086,56 +8080,56 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="44"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="33" t="str">
+      <c r="A25" s="29" t="str">
         <f>IF('UC4'!A2="","",'UC4'!A2)</f>
         <v>GL-0004</v>
       </c>
-      <c r="B25" s="35" t="str">
+      <c r="B25" t="str">
         <f>IF('UC4'!B2="","",'UC4'!B2)</f>
         <v>Olivia Brown</v>
       </c>
-      <c r="C25" s="35" t="str">
+      <c r="C25" t="str">
         <f>IF('UC4'!C2="","",'UC4'!C2)</f>
         <v>RESULT_NOT_RETURNED</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="8">
         <f>IF('UC4'!E2="","",'UC4'!E2)</f>
-        <v>46087</v>
-      </c>
-      <c r="E25" s="46" t="str">
+        <v>46176</v>
+      </c>
+      <c r="E25" s="35" t="str">
         <f>IF('UC4'!D2="","",'UC4'!D2)</f>
         <v>Result OBS-0010 reported 2026-06-03 has no delivery record to a clinic</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="47"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="36"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="37" t="str">
+      <c r="A26" s="31" t="str">
         <f>IF('UC4'!A3="","",'UC4'!A3)</f>
         <v>GL-0005</v>
       </c>
@@ -8147,19 +8141,19 @@
         <f>IF('UC4'!C3="","",'UC4'!C3)</f>
         <v>MULTI_PHARMACY_OVERLAP</v>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="34">
         <f>IF('UC4'!E3="","",'UC4'!E3)</f>
         <v>46132</v>
       </c>
-      <c r="E26" s="49" t="str">
+      <c r="E26" s="37" t="str">
         <f>IF('UC4'!D3="","",'UC4'!D3)</f>
         <v>biguanide supplied by pharmacies 1 and 2 with overlapping supply from 2026-04-20</v>
       </c>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="50"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="6">
